--- a/data/raw/pmi_official_history.xlsx
+++ b/data/raw/pmi_official_history.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Item</t>
   </si>
@@ -104,13 +104,43 @@
   <si>
     <t>france_flash</t>
   </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">euro_area_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">euro_area_flash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">germany_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">france_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spain_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uk_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">italy_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">germany_flash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">france_flash</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -122,14 +152,17 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -157,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -166,6 +199,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8412,34 +8446,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -8449,6 +8483,14 @@
       <c r="B2" t="n">
         <v>54.61</v>
       </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -8457,9 +8499,16 @@
       <c r="B3" t="n">
         <v>55.53</v>
       </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
       <c r="F3" t="n">
         <v>62.98</v>
       </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -8468,9 +8517,16 @@
       <c r="B4" t="n">
         <v>56.23</v>
       </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
       <c r="F4" t="n">
         <v>62.7</v>
       </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -8479,9 +8535,16 @@
       <c r="B5" t="n">
         <v>57.33</v>
       </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
       <c r="F5" t="n">
         <v>61.74</v>
       </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -8490,9 +8553,16 @@
       <c r="B6" t="n">
         <v>56.48</v>
       </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
       <c r="F6" t="n">
         <v>59.68</v>
       </c>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -8501,9 +8571,16 @@
       <c r="B7" t="n">
         <v>55.9</v>
       </c>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
       <c r="F7" t="n">
         <v>58.54</v>
       </c>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -8512,9 +8589,16 @@
       <c r="B8" t="n">
         <v>54.96</v>
       </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
       <c r="F8" t="n">
         <v>56.94</v>
       </c>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -8523,9 +8607,16 @@
       <c r="B9" t="n">
         <v>53.92</v>
       </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
       <c r="F9" t="n">
         <v>55.38</v>
       </c>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -8534,9 +8625,16 @@
       <c r="B10" t="n">
         <v>51.69</v>
       </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
       <c r="F10" t="n">
         <v>54.46</v>
       </c>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -8545,9 +8643,16 @@
       <c r="B11" t="n">
         <v>49.4</v>
       </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
       <c r="F11" t="n">
         <v>52.26</v>
       </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -8556,9 +8661,16 @@
       <c r="B12" t="n">
         <v>47.55</v>
       </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
       <c r="F12" t="n">
         <v>49.04</v>
       </c>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -8567,9 +8679,16 @@
       <c r="B13" t="n">
         <v>47.3</v>
       </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
       <c r="F13" t="n">
         <v>49.42</v>
       </c>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -8578,9 +8697,16 @@
       <c r="B14" t="n">
         <v>48.19</v>
       </c>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
       <c r="F14" t="n">
         <v>50.08</v>
       </c>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -8589,9 +8715,16 @@
       <c r="B15" t="n">
         <v>49.33</v>
       </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
       <c r="F15" t="n">
         <v>50.83</v>
       </c>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -8600,9 +8733,16 @@
       <c r="B16" t="n">
         <v>50.25</v>
       </c>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
       <c r="F16" t="n">
         <v>51.38</v>
       </c>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -8611,9 +8751,16 @@
       <c r="B17" t="n">
         <v>51.22</v>
       </c>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
       <c r="F17" t="n">
         <v>52.86</v>
       </c>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -8622,9 +8769,16 @@
       <c r="B18" t="n">
         <v>51.39</v>
       </c>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
       <c r="F18" t="n">
         <v>53.16</v>
       </c>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -8633,9 +8787,16 @@
       <c r="B19" t="n">
         <v>52.44</v>
       </c>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
       <c r="F19" t="n">
         <v>54.5</v>
       </c>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -8644,9 +8805,16 @@
       <c r="B20" t="n">
         <v>53.7</v>
       </c>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
       <c r="F20" t="n">
         <v>55.14</v>
       </c>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -8655,9 +8823,16 @@
       <c r="B21" t="n">
         <v>54.48</v>
       </c>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
       <c r="F21" t="n">
         <v>54.5</v>
       </c>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -8666,9 +8841,16 @@
       <c r="B22" t="n">
         <v>55.55</v>
       </c>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
       <c r="F22" t="n">
         <v>55.02</v>
       </c>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -8677,9 +8859,16 @@
       <c r="B23" t="n">
         <v>57.09</v>
       </c>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
       <c r="F23" t="n">
         <v>57.76</v>
       </c>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -8688,9 +8877,16 @@
       <c r="B24" t="n">
         <v>57.32</v>
       </c>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
       <c r="F24" t="n">
         <v>57.57</v>
       </c>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -8699,9 +8895,16 @@
       <c r="B25" t="n">
         <v>57.59</v>
       </c>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
       <c r="F25" t="n">
         <v>57.69</v>
       </c>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -8710,9 +8913,16 @@
       <c r="B26" t="n">
         <v>55.69</v>
       </c>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
       <c r="F26" t="n">
         <v>56.86</v>
       </c>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -8721,9 +8931,16 @@
       <c r="B27" t="n">
         <v>57.06</v>
       </c>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
       <c r="F27" t="n">
         <v>57.19</v>
       </c>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -8732,9 +8949,16 @@
       <c r="B28" t="n">
         <v>59.09</v>
       </c>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
       <c r="F28" t="n">
         <v>57.5</v>
       </c>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -8743,9 +8967,16 @@
       <c r="B29" t="n">
         <v>60.47</v>
       </c>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
       <c r="F29" t="n">
         <v>57</v>
       </c>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -8754,9 +8985,16 @@
       <c r="B30" t="n">
         <v>59.67</v>
       </c>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
       <c r="F30" t="n">
         <v>56.36</v>
       </c>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -8765,9 +9003,16 @@
       <c r="B31" t="n">
         <v>59.37</v>
       </c>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
       <c r="F31" t="n">
         <v>55.73</v>
       </c>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -8776,9 +9021,16 @@
       <c r="B32" t="n">
         <v>58.8</v>
       </c>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
       <c r="F32" t="n">
         <v>54.48</v>
       </c>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -8787,9 +9039,16 @@
       <c r="B33" t="n">
         <v>58.2</v>
       </c>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
       <c r="F33" t="n">
         <v>54.11</v>
       </c>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -8798,9 +9057,16 @@
       <c r="B34" t="n">
         <v>56.89</v>
       </c>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
       <c r="F34" t="n">
         <v>54.12</v>
       </c>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -8809,9 +9075,16 @@
       <c r="B35" t="n">
         <v>55.53</v>
       </c>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
       <c r="F35" t="n">
         <v>52.94</v>
       </c>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -8820,9 +9093,16 @@
       <c r="B36" t="n">
         <v>54.58</v>
       </c>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
       <c r="F36" t="n">
         <v>52.73</v>
       </c>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -8831,9 +9111,16 @@
       <c r="B37" t="n">
         <v>53.46</v>
       </c>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
       <c r="F37" t="n">
         <v>52.28</v>
       </c>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -8842,9 +9129,16 @@
       <c r="B38" t="n">
         <v>52.93</v>
       </c>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
       <c r="F38" t="n">
         <v>51.58</v>
       </c>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -8853,9 +9147,16 @@
       <c r="B39" t="n">
         <v>52.32</v>
       </c>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
       <c r="F39" t="n">
         <v>50.51</v>
       </c>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -8864,9 +9165,16 @@
       <c r="B40" t="n">
         <v>51.19</v>
       </c>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
       <c r="F40" t="n">
         <v>50.16</v>
       </c>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -8875,9 +9183,16 @@
       <c r="B41" t="n">
         <v>49.23</v>
       </c>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
       <c r="F41" t="n">
         <v>48.69</v>
       </c>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -8886,9 +9201,16 @@
       <c r="B42" t="n">
         <v>48.51</v>
       </c>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
       <c r="F42" t="n">
         <v>48.73</v>
       </c>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -8897,9 +9219,16 @@
       <c r="B43" t="n">
         <v>47.83</v>
       </c>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
       <c r="F43" t="n">
         <v>49.45</v>
       </c>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -8908,12 +9237,18 @@
       <c r="B44" t="n">
         <v>47.27</v>
       </c>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
       <c r="F44" t="n">
         <v>49.54</v>
       </c>
       <c r="G44" t="n">
         <v>47</v>
       </c>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -8922,12 +9257,18 @@
       <c r="B45" t="n">
         <v>47.51</v>
       </c>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
       <c r="F45" t="n">
         <v>49.73</v>
       </c>
       <c r="G45" t="n">
         <v>46.4</v>
       </c>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -8936,12 +9277,18 @@
       <c r="B46" t="n">
         <v>45.95</v>
       </c>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
       <c r="F46" t="n">
         <v>48.49</v>
       </c>
       <c r="G46" t="n">
         <v>46.5</v>
       </c>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -8950,12 +9297,18 @@
       <c r="B47" t="n">
         <v>42.94</v>
       </c>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
       <c r="F47" t="n">
         <v>45.21</v>
       </c>
       <c r="G47" t="n">
         <v>46.5</v>
       </c>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -8964,12 +9317,18 @@
       <c r="B48" t="n">
         <v>43.6</v>
       </c>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
       <c r="F48" t="n">
         <v>43.44</v>
       </c>
       <c r="G48" t="n">
         <v>45.6</v>
       </c>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -8978,12 +9337,18 @@
       <c r="B49" t="n">
         <v>44.12</v>
       </c>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
       <c r="F49" t="n">
         <v>43.87</v>
       </c>
       <c r="G49" t="n">
         <v>45.2</v>
       </c>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -8992,12 +9357,18 @@
       <c r="B50" t="n">
         <v>46.31</v>
       </c>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
       <c r="F50" t="n">
         <v>47.58</v>
       </c>
       <c r="G50" t="n">
         <v>46.5</v>
       </c>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -9006,12 +9377,18 @@
       <c r="B51" t="n">
         <v>48.56</v>
       </c>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
       <c r="F51" t="n">
         <v>48.37</v>
       </c>
       <c r="G51" t="n">
         <v>50.2</v>
       </c>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -9020,12 +9397,18 @@
       <c r="B52" t="n">
         <v>49.95</v>
       </c>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
       <c r="F52" t="n">
         <v>50.13</v>
       </c>
       <c r="G52" t="n">
         <v>50.6</v>
       </c>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -9034,12 +9417,18 @@
       <c r="B53" t="n">
         <v>50.75</v>
       </c>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
       <c r="F53" t="n">
         <v>52.17</v>
       </c>
       <c r="G53" t="n">
         <v>53.2</v>
       </c>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -9048,12 +9437,18 @@
       <c r="B54" t="n">
         <v>51.68</v>
       </c>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
       <c r="F54" t="n">
         <v>54.22</v>
       </c>
       <c r="G54" t="n">
         <v>52.7</v>
       </c>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -9062,12 +9457,18 @@
       <c r="B55" t="n">
         <v>51.78</v>
       </c>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
       <c r="F55" t="n">
         <v>52.73</v>
       </c>
       <c r="G55" t="n">
         <v>50.6</v>
       </c>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -9076,12 +9477,18 @@
       <c r="B56" t="n">
         <v>51.59</v>
       </c>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
       <c r="F56" t="n">
         <v>51.62</v>
       </c>
       <c r="G56" t="n">
         <v>49.1</v>
       </c>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -9090,12 +9497,18 @@
       <c r="B57" t="n">
         <v>50.83</v>
       </c>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
       <c r="F57" t="n">
         <v>51.55</v>
       </c>
       <c r="G57" t="n">
         <v>51</v>
       </c>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -9104,12 +9517,18 @@
       <c r="B58" t="n">
         <v>48.9</v>
       </c>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
       <c r="F58" t="n">
         <v>50.5</v>
       </c>
       <c r="G58" t="n">
         <v>50.3</v>
       </c>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -9118,12 +9537,18 @@
       <c r="B59" t="n">
         <v>49.15</v>
       </c>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
       <c r="F59" t="n">
         <v>49.58</v>
       </c>
       <c r="G59" t="n">
         <v>50.6</v>
       </c>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -9132,12 +9557,18 @@
       <c r="B60" t="n">
         <v>49.42</v>
       </c>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
       <c r="F60" t="n">
         <v>48.93</v>
       </c>
       <c r="G60" t="n">
         <v>50.1</v>
       </c>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -9146,12 +9577,18 @@
       <c r="B61" t="n">
         <v>48.42</v>
       </c>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
       <c r="F61" t="n">
         <v>47.27</v>
       </c>
       <c r="G61" t="n">
         <v>49.3</v>
       </c>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -9160,12 +9597,18 @@
       <c r="B62" t="n">
         <v>49.35</v>
       </c>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
       <c r="F62" t="n">
         <v>48.06</v>
       </c>
       <c r="G62" t="n">
         <v>48.7</v>
       </c>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -9174,12 +9617,18 @@
       <c r="B63" t="n">
         <v>50.1</v>
       </c>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
       <c r="F63" t="n">
         <v>48.56</v>
       </c>
       <c r="G63" t="n">
         <v>48.1</v>
       </c>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -9188,12 +9637,18 @@
       <c r="B64" t="n">
         <v>48.42</v>
       </c>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
       <c r="F64" t="n">
         <v>48.45</v>
       </c>
       <c r="G64" t="n">
         <v>46.3</v>
       </c>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -9202,12 +9657,18 @@
       <c r="B65" t="n">
         <v>47.84</v>
       </c>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
       <c r="F65" t="n">
         <v>48.46</v>
       </c>
       <c r="G65" t="n">
         <v>48.6</v>
       </c>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -9216,12 +9677,18 @@
       <c r="B66" t="n">
         <v>46.86</v>
       </c>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
       <c r="F66" t="n">
         <v>48.45</v>
       </c>
       <c r="G66" t="n">
         <v>48.3</v>
       </c>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -9230,12 +9697,18 @@
       <c r="B67" t="n">
         <v>46.66</v>
       </c>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
       <c r="F67" t="n">
         <v>48.2</v>
       </c>
       <c r="G67" t="n">
         <v>49.5</v>
       </c>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -9244,12 +9717,18 @@
       <c r="B68" t="n">
         <v>48.05</v>
       </c>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
       <c r="F68" t="n">
         <v>48.36</v>
       </c>
       <c r="G68" t="n">
         <v>51.1</v>
       </c>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -9258,12 +9737,18 @@
       <c r="B69" t="n">
         <v>49.14</v>
       </c>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
       <c r="F69" t="n">
         <v>49.35</v>
       </c>
       <c r="G69" t="n">
         <v>52.2</v>
       </c>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -9272,12 +9757,18 @@
       <c r="B70" t="n">
         <v>50.09</v>
       </c>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
       <c r="F70" t="n">
         <v>50.69</v>
       </c>
       <c r="G70" t="n">
         <v>53.2</v>
       </c>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -9286,12 +9777,18 @@
       <c r="B71" t="n">
         <v>51.32</v>
       </c>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
       <c r="F71" t="n">
         <v>50.28</v>
       </c>
       <c r="G71" t="n">
         <v>54.3</v>
       </c>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -9300,12 +9797,18 @@
       <c r="B72" t="n">
         <v>52.15</v>
       </c>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
       <c r="F72" t="n">
         <v>52.63</v>
       </c>
       <c r="G72" t="n">
         <v>54.7</v>
       </c>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -9314,12 +9817,18 @@
       <c r="B73" t="n">
         <v>52.41</v>
       </c>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
       <c r="F73" t="n">
         <v>51.83</v>
       </c>
       <c r="G73" t="n">
         <v>56</v>
       </c>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -9328,12 +9837,18 @@
       <c r="B74" t="n">
         <v>52.54</v>
       </c>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
       <c r="F74" t="n">
         <v>51.88</v>
       </c>
       <c r="G74" t="n">
         <v>55.8</v>
       </c>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -9342,12 +9857,18 @@
       <c r="B75" t="n">
         <v>52.47</v>
       </c>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
       <c r="F75" t="n">
         <v>53.22</v>
       </c>
       <c r="G75" t="n">
         <v>53</v>
       </c>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -9356,12 +9877,18 @@
       <c r="B76" t="n">
         <v>53.26</v>
       </c>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
       <c r="F76" t="n">
         <v>52.92</v>
       </c>
       <c r="G76" t="n">
         <v>53.8</v>
       </c>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -9370,12 +9897,18 @@
       <c r="B77" t="n">
         <v>53.95</v>
       </c>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
       <c r="F77" t="n">
         <v>53.59</v>
       </c>
       <c r="G77" t="n">
         <v>55.2</v>
       </c>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -9384,12 +9917,18 @@
       <c r="B78" t="n">
         <v>54.71</v>
       </c>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
       <c r="F78" t="n">
         <v>53.03</v>
       </c>
       <c r="G78" t="n">
         <v>55.7</v>
       </c>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -9398,12 +9937,18 @@
       <c r="B79" t="n">
         <v>54.44</v>
       </c>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
       <c r="F79" t="n">
         <v>51.13</v>
       </c>
       <c r="G79" t="n">
         <v>55</v>
       </c>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -9412,12 +9957,18 @@
       <c r="B80" t="n">
         <v>54.65</v>
       </c>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
       <c r="F80" t="n">
         <v>51.47</v>
       </c>
       <c r="G80" t="n">
         <v>56</v>
       </c>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -9426,12 +9977,18 @@
       <c r="B81" t="n">
         <v>53.85</v>
       </c>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
       <c r="F81" t="n">
         <v>51.66</v>
       </c>
       <c r="G81" t="n">
         <v>52.8</v>
       </c>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -9440,12 +9997,18 @@
       <c r="B82" t="n">
         <v>53.13</v>
       </c>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
       <c r="F82" t="n">
         <v>51.08</v>
       </c>
       <c r="G82" t="n">
         <v>52.3</v>
       </c>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -9454,12 +10017,18 @@
       <c r="B83" t="n">
         <v>52.38</v>
       </c>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
       <c r="F83" t="n">
         <v>51.31</v>
       </c>
       <c r="G83" t="n">
         <v>53.5</v>
       </c>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -9468,12 +10037,18 @@
       <c r="B84" t="n">
         <v>50.43</v>
       </c>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
       <c r="F84" t="n">
         <v>51.71</v>
       </c>
       <c r="G84" t="n">
         <v>55</v>
       </c>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -9482,12 +10057,18 @@
       <c r="B85" t="n">
         <v>51.44</v>
       </c>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
       <c r="F85" t="n">
         <v>52.89</v>
       </c>
       <c r="G85" t="n">
         <v>53.3</v>
       </c>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -9496,12 +10077,18 @@
       <c r="B86" t="n">
         <v>51.87</v>
       </c>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
       <c r="F86" t="n">
         <v>53.62</v>
       </c>
       <c r="G86" t="n">
         <v>51.8</v>
       </c>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -9510,12 +10097,18 @@
       <c r="B87" t="n">
         <v>51.9</v>
       </c>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
       <c r="F87" t="n">
         <v>52.92</v>
       </c>
       <c r="G87" t="n">
         <v>51.6</v>
       </c>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -9524,12 +10117,18 @@
       <c r="B88" t="n">
         <v>50.4</v>
       </c>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
       <c r="F88" t="n">
         <v>50.48</v>
       </c>
       <c r="G88" t="n">
         <v>51.6</v>
       </c>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -9538,12 +10137,18 @@
       <c r="B89" t="n">
         <v>49.19</v>
       </c>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
       <c r="F89" t="n">
         <v>49.2</v>
       </c>
       <c r="G89" t="n">
         <v>49.1</v>
       </c>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -9552,12 +10157,18 @@
       <c r="B90" t="n">
         <v>48.7</v>
       </c>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
       <c r="F90" t="n">
         <v>48.52</v>
       </c>
       <c r="G90" t="n">
         <v>47</v>
       </c>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -9566,12 +10177,18 @@
       <c r="B91" t="n">
         <v>49.91</v>
       </c>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
       <c r="F91" t="n">
         <v>49.3</v>
       </c>
       <c r="G91" t="n">
         <v>49.6</v>
       </c>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -9580,12 +10197,18 @@
       <c r="B92" t="n">
         <v>50.81</v>
       </c>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
       <c r="F92" t="n">
         <v>50.93</v>
       </c>
       <c r="G92" t="n">
         <v>49.5</v>
       </c>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -9594,12 +10217,18 @@
       <c r="B93" t="n">
         <v>50.43</v>
       </c>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
       <c r="F93" t="n">
         <v>51.38</v>
       </c>
       <c r="G93" t="n">
         <v>50.3</v>
       </c>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -9608,12 +10237,18 @@
       <c r="B94" t="n">
         <v>51.74</v>
       </c>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
       <c r="F94" t="n">
         <v>52.06</v>
       </c>
       <c r="G94" t="n">
         <v>51.5</v>
       </c>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -9622,12 +10257,18 @@
       <c r="B95" t="n">
         <v>52.69</v>
       </c>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
       <c r="F95" t="n">
         <v>52.16</v>
       </c>
       <c r="G95" t="n">
         <v>51.6</v>
       </c>
+      <c r="H95"/>
+      <c r="I95"/>
+      <c r="J95"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -9636,12 +10277,18 @@
       <c r="B96" t="n">
         <v>52.76</v>
       </c>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
       <c r="F96" t="n">
         <v>52.35</v>
       </c>
       <c r="G96" t="n">
         <v>51</v>
       </c>
+      <c r="H96"/>
+      <c r="I96"/>
+      <c r="J96"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -9650,12 +10297,18 @@
       <c r="B97" t="n">
         <v>53.58</v>
       </c>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
       <c r="F97" t="n">
         <v>53.03</v>
       </c>
       <c r="G97" t="n">
         <v>51.3</v>
       </c>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -9664,12 +10317,18 @@
       <c r="B98" t="n">
         <v>53.49</v>
       </c>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
       <c r="F98" t="n">
         <v>52.61</v>
       </c>
       <c r="G98" t="n">
         <v>51.8</v>
       </c>
+      <c r="H98"/>
+      <c r="I98"/>
+      <c r="J98"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -9678,12 +10337,18 @@
       <c r="B99" t="n">
         <v>54.46</v>
       </c>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
       <c r="F99" t="n">
         <v>52.75</v>
       </c>
       <c r="G99" t="n">
         <v>51.5</v>
       </c>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -9692,12 +10357,18 @@
       <c r="B100" t="n">
         <v>56.08</v>
       </c>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
       <c r="F100" t="n">
         <v>54.74</v>
       </c>
       <c r="G100" t="n">
         <v>50.9</v>
       </c>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -9706,12 +10377,18 @@
       <c r="B101" t="n">
         <v>56.73</v>
       </c>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
       <c r="F101" t="n">
         <v>54.33</v>
       </c>
       <c r="G101" t="n">
         <v>54.1</v>
       </c>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -9720,12 +10397,18 @@
       <c r="B102" t="n">
         <v>57.02</v>
       </c>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
       <c r="F102" t="n">
         <v>55.59</v>
       </c>
       <c r="G102" t="n">
         <v>53.3</v>
       </c>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -9734,12 +10417,18 @@
       <c r="B103" t="n">
         <v>57.68</v>
       </c>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
       <c r="F103" t="n">
         <v>55.74</v>
       </c>
       <c r="G103" t="n">
         <v>55</v>
       </c>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -9748,12 +10437,18 @@
       <c r="B104" t="n">
         <v>57.38</v>
       </c>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
       <c r="F104" t="n">
         <v>55.02</v>
       </c>
       <c r="G104" t="n">
         <v>53.7</v>
       </c>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -9762,12 +10457,18 @@
       <c r="B105" t="n">
         <v>56.54</v>
       </c>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
       <c r="F105" t="n">
         <v>54.64</v>
       </c>
       <c r="G105" t="n">
         <v>52.9</v>
       </c>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -9776,12 +10477,18 @@
       <c r="B106" t="n">
         <v>56.64</v>
       </c>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
       <c r="F106" t="n">
         <v>55.64</v>
       </c>
       <c r="G106" t="n">
         <v>54.5</v>
       </c>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -9790,12 +10497,18 @@
       <c r="B107" t="n">
         <v>57</v>
       </c>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
       <c r="F107" t="n">
         <v>57.03</v>
       </c>
       <c r="G107" t="n">
         <v>53.7</v>
       </c>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -9804,12 +10517,18 @@
       <c r="B108" t="n">
         <v>56.56</v>
       </c>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
       <c r="F108" t="n">
         <v>56.11</v>
       </c>
       <c r="G108" t="n">
         <v>52.7</v>
       </c>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -9818,12 +10537,18 @@
       <c r="B109" t="n">
         <v>56.52</v>
       </c>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
       <c r="F109" t="n">
         <v>57.17</v>
       </c>
       <c r="G109" t="n">
         <v>52.3</v>
       </c>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -9832,12 +10557,18 @@
       <c r="B110" t="n">
         <v>55.5</v>
       </c>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
       <c r="F110" t="n">
         <v>56.21</v>
       </c>
       <c r="G110" t="n">
         <v>53.2</v>
       </c>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -9846,12 +10577,18 @@
       <c r="B111" t="n">
         <v>55.62</v>
       </c>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
       <c r="F111" t="n">
         <v>56.22</v>
       </c>
       <c r="G111" t="n">
         <v>55.3</v>
       </c>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -9860,12 +10597,18 @@
       <c r="B112" t="n">
         <v>55.41</v>
       </c>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
       <c r="F112" t="n">
         <v>55.45</v>
       </c>
       <c r="G112" t="n">
         <v>54.2</v>
       </c>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -9874,12 +10617,18 @@
       <c r="B113" t="n">
         <v>55.38</v>
       </c>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
       <c r="F113" t="n">
         <v>55.98</v>
       </c>
       <c r="G113" t="n">
         <v>54</v>
       </c>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -9888,12 +10637,18 @@
       <c r="B114" t="n">
         <v>55.01</v>
       </c>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
       <c r="F114" t="n">
         <v>53.31</v>
       </c>
       <c r="G114" t="n">
         <v>54.8</v>
       </c>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -9902,12 +10657,18 @@
       <c r="B115" t="n">
         <v>55.56</v>
       </c>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
       <c r="F115" t="n">
         <v>55.05</v>
       </c>
       <c r="G115" t="n">
         <v>54.7</v>
       </c>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -9916,12 +10677,18 @@
       <c r="B116" t="n">
         <v>54.9</v>
       </c>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
       <c r="F116" t="n">
         <v>53.22</v>
       </c>
       <c r="G116" t="n">
         <v>55.7</v>
       </c>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -9930,12 +10697,18 @@
       <c r="B117" t="n">
         <v>54.34</v>
       </c>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
       <c r="F117" t="n">
         <v>52.16</v>
       </c>
       <c r="G117" t="n">
         <v>56.1</v>
       </c>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -9944,12 +10717,18 @@
       <c r="B118" t="n">
         <v>53.21</v>
       </c>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
       <c r="F118" t="n">
         <v>50.8</v>
       </c>
       <c r="G118" t="n">
         <v>54.7</v>
       </c>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -9958,12 +10737,18 @@
       <c r="B119" t="n">
         <v>51.52</v>
       </c>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
       <c r="F119" t="n">
         <v>49.58</v>
       </c>
       <c r="G119" t="n">
         <v>52.8</v>
       </c>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -9972,12 +10757,18 @@
       <c r="B120" t="n">
         <v>52.8</v>
       </c>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
       <c r="F120" t="n">
         <v>50.73</v>
       </c>
       <c r="G120" t="n">
         <v>54.3</v>
       </c>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -9986,12 +10777,18 @@
       <c r="B121" t="n">
         <v>52.56</v>
       </c>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
       <c r="F121" t="n">
         <v>49.51</v>
       </c>
       <c r="G121" t="n">
         <v>52.4</v>
       </c>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -10000,12 +10797,18 @@
       <c r="B122" t="n">
         <v>52.77</v>
       </c>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
       <c r="F122" t="n">
         <v>49.77</v>
       </c>
       <c r="G122" t="n">
         <v>50.7</v>
       </c>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -10014,12 +10817,18 @@
       <c r="B123" t="n">
         <v>52.34</v>
       </c>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
       <c r="F123" t="n">
         <v>46.72</v>
       </c>
       <c r="G123" t="n">
         <v>51.3</v>
       </c>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -10028,12 +10837,18 @@
       <c r="B124" t="n">
         <v>52.03</v>
       </c>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
       <c r="F124" t="n">
         <v>46.42</v>
       </c>
       <c r="G124" t="n">
         <v>51.3</v>
       </c>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -10042,12 +10857,18 @@
       <c r="B125" t="n">
         <v>50.74</v>
       </c>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
       <c r="F125" t="n">
         <v>45.19</v>
       </c>
       <c r="G125" t="n">
         <v>50.8</v>
       </c>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -10056,12 +10877,18 @@
       <c r="B126" t="n">
         <v>50.6</v>
       </c>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
       <c r="F126" t="n">
         <v>43.79</v>
       </c>
       <c r="G126" t="n">
         <v>49.5</v>
       </c>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -10070,12 +10897,18 @@
       <c r="B127" t="n">
         <v>49.16</v>
       </c>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
       <c r="F127" t="n">
         <v>40.61</v>
       </c>
       <c r="G127" t="n">
         <v>45.9</v>
       </c>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -10084,12 +10917,18 @@
       <c r="B128" t="n">
         <v>47.38</v>
       </c>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
       <c r="F128" t="n">
         <v>39.2</v>
       </c>
       <c r="G128" t="n">
         <v>44.1</v>
       </c>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -10098,12 +10937,18 @@
       <c r="B129" t="n">
         <v>47.55</v>
       </c>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
       <c r="F129" t="n">
         <v>42.4</v>
       </c>
       <c r="G129" t="n">
         <v>45.3</v>
       </c>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -10112,12 +10957,18 @@
       <c r="B130" t="n">
         <v>44.97</v>
       </c>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
       <c r="F130" t="n">
         <v>38.32</v>
       </c>
       <c r="G130" t="n">
         <v>41.2</v>
       </c>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -10126,12 +10977,18 @@
       <c r="B131" t="n">
         <v>41.1</v>
       </c>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
       <c r="F131" t="n">
         <v>34.6</v>
       </c>
       <c r="G131" t="n">
         <v>40.7</v>
       </c>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -10140,12 +10997,18 @@
       <c r="B132" t="n">
         <v>35.58</v>
       </c>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
       <c r="F132" t="n">
         <v>29.42</v>
       </c>
       <c r="G132" t="n">
         <v>34.5</v>
       </c>
+      <c r="H132"/>
+      <c r="I132"/>
+      <c r="J132"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -10154,12 +11017,18 @@
       <c r="B133" t="n">
         <v>33.87</v>
       </c>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
       <c r="F133" t="n">
         <v>28.49</v>
       </c>
       <c r="G133" t="n">
         <v>34.9</v>
       </c>
+      <c r="H133"/>
+      <c r="I133"/>
+      <c r="J133"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -10168,12 +11037,18 @@
       <c r="B134" t="n">
         <v>34.42</v>
       </c>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
       <c r="F134" t="n">
         <v>31.51</v>
       </c>
       <c r="G134" t="n">
         <v>35.8</v>
       </c>
+      <c r="H134"/>
+      <c r="I134"/>
+      <c r="J134"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -10182,12 +11057,18 @@
       <c r="B135" t="n">
         <v>33.55</v>
       </c>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
       <c r="F135" t="n">
         <v>31.85</v>
       </c>
       <c r="G135" t="n">
         <v>34.7</v>
       </c>
+      <c r="H135"/>
+      <c r="I135"/>
+      <c r="J135"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -10196,12 +11077,18 @@
       <c r="B136" t="n">
         <v>33.93</v>
       </c>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
       <c r="F136" t="n">
         <v>32.92</v>
       </c>
       <c r="G136" t="n">
         <v>39.5</v>
       </c>
+      <c r="H136"/>
+      <c r="I136"/>
+      <c r="J136"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -10210,12 +11097,18 @@
       <c r="B137" t="n">
         <v>36.83</v>
       </c>
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="E137"/>
       <c r="F137" t="n">
         <v>34.61</v>
       </c>
       <c r="G137" t="n">
         <v>43.1</v>
       </c>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -10224,12 +11117,18 @@
       <c r="B138" t="n">
         <v>40.68</v>
       </c>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
       <c r="F138" t="n">
         <v>39.83</v>
       </c>
       <c r="G138" t="n">
         <v>45.4</v>
       </c>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -10238,12 +11137,18 @@
       <c r="B139" t="n">
         <v>42.62</v>
       </c>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
       <c r="F139" t="n">
         <v>42.76</v>
       </c>
       <c r="G139" t="n">
         <v>47.4</v>
       </c>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -10252,12 +11157,18 @@
       <c r="B140" t="n">
         <v>46.25</v>
       </c>
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="E140"/>
       <c r="F140" t="n">
         <v>47.33</v>
       </c>
       <c r="G140" t="n">
         <v>50.2</v>
       </c>
+      <c r="H140"/>
+      <c r="I140"/>
+      <c r="J140"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -10266,12 +11177,18 @@
       <c r="B141" t="n">
         <v>48.24</v>
       </c>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
       <c r="F141" t="n">
         <v>47.2</v>
       </c>
       <c r="G141" t="n">
         <v>49.7</v>
       </c>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -10280,12 +11197,18 @@
       <c r="B142" t="n">
         <v>49.29</v>
       </c>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
       <c r="F142" t="n">
         <v>45.82</v>
       </c>
       <c r="G142" t="n">
         <v>49.9</v>
       </c>
+      <c r="H142"/>
+      <c r="I142"/>
+      <c r="J142"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -10294,12 +11217,18 @@
       <c r="B143" t="n">
         <v>50.73</v>
       </c>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
       <c r="F143" t="n">
         <v>46.3</v>
       </c>
       <c r="G143" t="n">
         <v>53.4</v>
       </c>
+      <c r="H143"/>
+      <c r="I143"/>
+      <c r="J143"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -10308,12 +11237,18 @@
       <c r="B144" t="n">
         <v>51.2</v>
       </c>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
       <c r="F144" t="n">
         <v>45.28</v>
       </c>
       <c r="G144" t="n">
         <v>51.8</v>
       </c>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -10322,12 +11257,18 @@
       <c r="B145" t="n">
         <v>51.59</v>
       </c>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
       <c r="F145" t="n">
         <v>45.19</v>
       </c>
       <c r="G145" t="n">
         <v>54.6</v>
       </c>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -10336,12 +11277,18 @@
       <c r="B146" t="n">
         <v>52.39</v>
       </c>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
       <c r="F146" t="n">
         <v>45.27</v>
       </c>
       <c r="G146" t="n">
         <v>56.6</v>
       </c>
+      <c r="H146"/>
+      <c r="I146"/>
+      <c r="J146"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -10350,12 +11297,18 @@
       <c r="B147" t="n">
         <v>54.23</v>
       </c>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
       <c r="F147" t="n">
         <v>49.1</v>
       </c>
       <c r="G147" t="n">
         <v>56.5</v>
       </c>
+      <c r="H147"/>
+      <c r="I147"/>
+      <c r="J147"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -10364,12 +11317,18 @@
       <c r="B148" t="n">
         <v>56.65</v>
       </c>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
       <c r="F148" t="n">
         <v>51.85</v>
       </c>
       <c r="G148" t="n">
         <v>57.3</v>
       </c>
+      <c r="H148"/>
+      <c r="I148"/>
+      <c r="J148"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -10378,12 +11337,18 @@
       <c r="B149" t="n">
         <v>57.57</v>
       </c>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
       <c r="F149" t="n">
         <v>53.31</v>
       </c>
       <c r="G149" t="n">
         <v>58</v>
       </c>
+      <c r="H149"/>
+      <c r="I149"/>
+      <c r="J149"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -10392,12 +11357,18 @@
       <c r="B150" t="n">
         <v>55.84</v>
       </c>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
       <c r="F150" t="n">
         <v>51.51</v>
       </c>
       <c r="G150" t="n">
         <v>58</v>
       </c>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -10406,12 +11377,18 @@
       <c r="B151" t="n">
         <v>55.64</v>
       </c>
+      <c r="C151"/>
+      <c r="D151"/>
+      <c r="E151"/>
       <c r="F151" t="n">
         <v>51.18</v>
       </c>
       <c r="G151" t="n">
         <v>57.6</v>
       </c>
+      <c r="H151"/>
+      <c r="I151"/>
+      <c r="J151"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -10420,12 +11397,18 @@
       <c r="B152" t="n">
         <v>56.69</v>
       </c>
+      <c r="C152"/>
+      <c r="D152"/>
+      <c r="E152"/>
       <c r="F152" t="n">
         <v>51.61</v>
       </c>
       <c r="G152" t="n">
         <v>56.9</v>
       </c>
+      <c r="H152"/>
+      <c r="I152"/>
+      <c r="J152"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -10434,12 +11417,18 @@
       <c r="B153" t="n">
         <v>55.1</v>
       </c>
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="E153"/>
       <c r="F153" t="n">
         <v>51.2</v>
       </c>
       <c r="G153" t="n">
         <v>53.7</v>
       </c>
+      <c r="H153"/>
+      <c r="I153"/>
+      <c r="J153"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -10448,12 +11437,18 @@
       <c r="B154" t="n">
         <v>53.66</v>
       </c>
+      <c r="C154"/>
+      <c r="D154"/>
+      <c r="E154"/>
       <c r="F154" t="n">
         <v>49.64</v>
       </c>
       <c r="G154" t="n">
         <v>53.5</v>
       </c>
+      <c r="H154"/>
+      <c r="I154"/>
+      <c r="J154"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -10462,12 +11457,18 @@
       <c r="B155" t="n">
         <v>54.6</v>
       </c>
+      <c r="C155"/>
+      <c r="D155"/>
+      <c r="E155"/>
       <c r="F155" t="n">
         <v>51.22</v>
       </c>
       <c r="G155" t="n">
         <v>55.4</v>
       </c>
+      <c r="H155"/>
+      <c r="I155"/>
+      <c r="J155"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
@@ -10476,12 +11477,18 @@
       <c r="B156" t="n">
         <v>55.33</v>
       </c>
+      <c r="C156"/>
+      <c r="D156"/>
+      <c r="E156"/>
       <c r="F156" t="n">
         <v>50.02</v>
       </c>
       <c r="G156" t="n">
         <v>57.5</v>
       </c>
+      <c r="H156"/>
+      <c r="I156"/>
+      <c r="J156"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -10490,12 +11497,18 @@
       <c r="B157" t="n">
         <v>57.11</v>
       </c>
+      <c r="C157"/>
+      <c r="D157"/>
+      <c r="E157"/>
       <c r="F157" t="n">
         <v>51.46</v>
       </c>
       <c r="G157" t="n">
         <v>58.7</v>
       </c>
+      <c r="H157"/>
+      <c r="I157"/>
+      <c r="J157"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -10504,12 +11517,18 @@
       <c r="B158" t="n">
         <v>57.2921</v>
       </c>
+      <c r="C158"/>
+      <c r="D158"/>
+      <c r="E158"/>
       <c r="F158" t="n">
         <v>51.9618</v>
       </c>
       <c r="G158" t="n">
         <v>61.5</v>
       </c>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -10518,12 +11537,18 @@
       <c r="B159" t="n">
         <v>59.0249</v>
       </c>
+      <c r="C159"/>
+      <c r="D159"/>
+      <c r="E159"/>
       <c r="F159" t="n">
         <v>52.1382</v>
       </c>
       <c r="G159" t="n">
         <v>60.9</v>
       </c>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -10532,12 +11557,18 @@
       <c r="B160" t="n">
         <v>57.4976</v>
       </c>
+      <c r="C160"/>
+      <c r="D160"/>
+      <c r="E160"/>
       <c r="F160" t="n">
         <v>51.6376</v>
       </c>
       <c r="G160" t="n">
         <v>56.7</v>
       </c>
+      <c r="H160"/>
+      <c r="I160"/>
+      <c r="J160"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -10546,12 +11577,18 @@
       <c r="B161" t="n">
         <v>57.9526</v>
       </c>
+      <c r="C161"/>
+      <c r="D161"/>
+      <c r="E161"/>
       <c r="F161" t="n">
         <v>50.5735</v>
       </c>
       <c r="G161" t="n">
         <v>54.4</v>
       </c>
+      <c r="H161"/>
+      <c r="I161"/>
+      <c r="J161"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
@@ -10560,12 +11597,18 @@
       <c r="B162" t="n">
         <v>54.6433</v>
       </c>
+      <c r="C162"/>
+      <c r="D162"/>
+      <c r="E162"/>
       <c r="F162" t="n">
         <v>48.2008</v>
       </c>
       <c r="G162" t="n">
         <v>53</v>
       </c>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
@@ -10574,12 +11617,18 @@
       <c r="B163" t="n">
         <v>52.0438</v>
       </c>
+      <c r="C163"/>
+      <c r="D163"/>
+      <c r="E163"/>
       <c r="F163" t="n">
         <v>47.3086</v>
       </c>
       <c r="G163" t="n">
         <v>52.1</v>
       </c>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -10588,12 +11637,18 @@
       <c r="B164" t="n">
         <v>50.3629</v>
       </c>
+      <c r="C164"/>
+      <c r="D164"/>
+      <c r="E164"/>
       <c r="F164" t="n">
         <v>45.6472</v>
       </c>
       <c r="G164" t="n">
         <v>50.2</v>
       </c>
+      <c r="H164"/>
+      <c r="I164"/>
+      <c r="J164"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -10602,12 +11657,18 @@
       <c r="B165" t="n">
         <v>48.9938</v>
       </c>
+      <c r="C165"/>
+      <c r="D165"/>
+      <c r="E165"/>
       <c r="F165" t="n">
         <v>45.3181</v>
       </c>
       <c r="G165" t="n">
         <v>49.4</v>
       </c>
+      <c r="H165"/>
+      <c r="I165"/>
+      <c r="J165"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -10616,12 +11677,18 @@
       <c r="B166" t="n">
         <v>48.5145</v>
       </c>
+      <c r="C166"/>
+      <c r="D166"/>
+      <c r="E166"/>
       <c r="F166" t="n">
         <v>43.7392</v>
       </c>
       <c r="G166" t="n">
         <v>50.5</v>
       </c>
+      <c r="H166"/>
+      <c r="I166"/>
+      <c r="J166"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -10630,12 +11697,18 @@
       <c r="B167" t="n">
         <v>47.0894</v>
       </c>
+      <c r="C167"/>
+      <c r="D167"/>
+      <c r="E167"/>
       <c r="F167" t="n">
         <v>43.9396</v>
       </c>
       <c r="G167" t="n">
         <v>48.9</v>
       </c>
+      <c r="H167"/>
+      <c r="I167"/>
+      <c r="J167"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -10644,12 +11717,18 @@
       <c r="B168" t="n">
         <v>46.3659</v>
       </c>
+      <c r="C168"/>
+      <c r="D168"/>
+      <c r="E168"/>
       <c r="F168" t="n">
         <v>43.7662</v>
       </c>
       <c r="G168" t="n">
         <v>47.2</v>
       </c>
+      <c r="H168"/>
+      <c r="I168"/>
+      <c r="J168"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -10658,12 +11737,18 @@
       <c r="B169" t="n">
         <v>46.9408</v>
       </c>
+      <c r="C169"/>
+      <c r="D169"/>
+      <c r="E169"/>
       <c r="F169" t="n">
         <v>43.6767</v>
       </c>
       <c r="G169" t="n">
         <v>48.9</v>
       </c>
+      <c r="H169"/>
+      <c r="I169"/>
+      <c r="J169"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -10672,12 +11757,18 @@
       <c r="B170" t="n">
         <v>48.7764</v>
       </c>
+      <c r="C170"/>
+      <c r="D170"/>
+      <c r="E170"/>
       <c r="F170" t="n">
         <v>45.0863</v>
       </c>
       <c r="G170" t="n">
         <v>50.8</v>
       </c>
+      <c r="H170"/>
+      <c r="I170"/>
+      <c r="J170"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -10686,12 +11777,18 @@
       <c r="B171" t="n">
         <v>48.9578</v>
       </c>
+      <c r="C171"/>
+      <c r="D171"/>
+      <c r="E171"/>
       <c r="F171" t="n">
         <v>44.9605</v>
       </c>
       <c r="G171" t="n">
         <v>50.9</v>
       </c>
+      <c r="H171"/>
+      <c r="I171"/>
+      <c r="J171"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -10700,12 +11797,18 @@
       <c r="B172" t="n">
         <v>47.7169</v>
       </c>
+      <c r="C172"/>
+      <c r="D172"/>
+      <c r="E172"/>
       <c r="F172" t="n">
         <v>44.5135</v>
       </c>
       <c r="G172" t="n">
         <v>52.7</v>
       </c>
+      <c r="H172"/>
+      <c r="I172"/>
+      <c r="J172"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -10714,12 +11817,18 @@
       <c r="B173" t="n">
         <v>45.8926</v>
       </c>
+      <c r="C173"/>
+      <c r="D173"/>
+      <c r="E173"/>
       <c r="F173" t="n">
         <v>43.4757</v>
       </c>
       <c r="G173" t="n">
         <v>50.1</v>
       </c>
+      <c r="H173"/>
+      <c r="I173"/>
+      <c r="J173"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -10728,12 +11837,18 @@
       <c r="B174" t="n">
         <v>45.1267</v>
       </c>
+      <c r="C174"/>
+      <c r="D174"/>
+      <c r="E174"/>
       <c r="F174" t="n">
         <v>41.9907</v>
       </c>
       <c r="G174" t="n">
         <v>46.6</v>
       </c>
+      <c r="H174"/>
+      <c r="I174"/>
+      <c r="J174"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -10742,12 +11857,18 @@
       <c r="B175" t="n">
         <v>45.0739</v>
       </c>
+      <c r="C175"/>
+      <c r="D175"/>
+      <c r="E175"/>
       <c r="F175" t="n">
         <v>41.0812</v>
       </c>
       <c r="G175" t="n">
         <v>48.5</v>
       </c>
+      <c r="H175"/>
+      <c r="I175"/>
+      <c r="J175"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -10756,12 +11877,18 @@
       <c r="B176" t="n">
         <v>43.9972</v>
       </c>
+      <c r="C176"/>
+      <c r="D176"/>
+      <c r="E176"/>
       <c r="F176" t="n">
         <v>42.2877</v>
       </c>
       <c r="G176" t="n">
         <v>45.4</v>
       </c>
+      <c r="H176"/>
+      <c r="I176"/>
+      <c r="J176"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -10770,12 +11897,18 @@
       <c r="B177" t="n">
         <v>45.0829</v>
       </c>
+      <c r="C177"/>
+      <c r="D177"/>
+      <c r="E177"/>
       <c r="F177" t="n">
         <v>44.049</v>
       </c>
       <c r="G177" t="n">
         <v>49.8</v>
       </c>
+      <c r="H177"/>
+      <c r="I177"/>
+      <c r="J177"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -10784,12 +11917,18 @@
       <c r="B178" t="n">
         <v>46.1417</v>
       </c>
+      <c r="C178"/>
+      <c r="D178"/>
+      <c r="E178"/>
       <c r="F178" t="n">
         <v>44.5478</v>
       </c>
       <c r="G178" t="n">
         <v>48.3</v>
       </c>
+      <c r="H178"/>
+      <c r="I178"/>
+      <c r="J178"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -10798,12 +11937,18 @@
       <c r="B179" t="n">
         <v>45.4483</v>
       </c>
+      <c r="C179"/>
+      <c r="D179"/>
+      <c r="E179"/>
       <c r="F179" t="n">
         <v>43.5182</v>
       </c>
       <c r="G179" t="n">
         <v>47.9</v>
       </c>
+      <c r="H179"/>
+      <c r="I179"/>
+      <c r="J179"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -10812,12 +11957,18 @@
       <c r="B180" t="n">
         <v>46.1604</v>
       </c>
+      <c r="C180"/>
+      <c r="D180"/>
+      <c r="E180"/>
       <c r="F180" t="n">
         <v>45.35</v>
       </c>
       <c r="G180" t="n">
         <v>48</v>
       </c>
+      <c r="H180"/>
+      <c r="I180"/>
+      <c r="J180"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -10826,12 +11977,18 @@
       <c r="B181" t="n">
         <v>46.0981</v>
       </c>
+      <c r="C181"/>
+      <c r="D181"/>
+      <c r="E181"/>
       <c r="F181" t="n">
         <v>44.5516</v>
       </c>
       <c r="G181" t="n">
         <v>50.8</v>
       </c>
+      <c r="H181"/>
+      <c r="I181"/>
+      <c r="J181"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -10840,12 +11997,18 @@
       <c r="B182" t="n">
         <v>47.9227</v>
       </c>
+      <c r="C182"/>
+      <c r="D182"/>
+      <c r="E182"/>
       <c r="F182" t="n">
         <v>46.0822</v>
       </c>
       <c r="G182" t="n">
         <v>51.1</v>
       </c>
+      <c r="H182"/>
+      <c r="I182"/>
+      <c r="J182"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -10854,12 +12017,18 @@
       <c r="B183" t="n">
         <v>47.9336</v>
       </c>
+      <c r="C183"/>
+      <c r="D183"/>
+      <c r="E183"/>
       <c r="F183" t="n">
         <v>46.7957</v>
       </c>
       <c r="G183" t="n">
         <v>47.9</v>
       </c>
+      <c r="H183"/>
+      <c r="I183"/>
+      <c r="J183"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -10868,12 +12037,18 @@
       <c r="B184" t="n">
         <v>46.7529</v>
       </c>
+      <c r="C184"/>
+      <c r="D184"/>
+      <c r="E184"/>
       <c r="F184" t="n">
         <v>44.155</v>
       </c>
       <c r="G184" t="n">
         <v>50</v>
       </c>
+      <c r="H184"/>
+      <c r="I184"/>
+      <c r="J184"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -10882,12 +12057,18 @@
       <c r="B185" t="n">
         <v>46.686</v>
       </c>
+      <c r="C185"/>
+      <c r="D185"/>
+      <c r="E185"/>
       <c r="F185" t="n">
         <v>44.7032</v>
       </c>
       <c r="G185" t="n">
         <v>50.5</v>
       </c>
+      <c r="H185"/>
+      <c r="I185"/>
+      <c r="J185"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -10896,6 +12077,7 @@
       <c r="B186" t="n">
         <v>48.319</v>
       </c>
+      <c r="C186"/>
       <c r="D186" t="n">
         <v>49.4</v>
       </c>
@@ -10911,6 +12093,8 @@
       <c r="H186" t="n">
         <v>47.3</v>
       </c>
+      <c r="I186"/>
+      <c r="J186"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -10919,6 +12103,7 @@
       <c r="B187" t="n">
         <v>48.8244</v>
       </c>
+      <c r="C187"/>
       <c r="D187" t="n">
         <v>48.6</v>
       </c>
@@ -10934,6 +12119,8 @@
       <c r="H187" t="n">
         <v>49.1</v>
       </c>
+      <c r="I187"/>
+      <c r="J187"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
@@ -10942,6 +12129,7 @@
       <c r="B188" t="n">
         <v>50.2878</v>
       </c>
+      <c r="C188"/>
       <c r="D188" t="n">
         <v>50.7</v>
       </c>
@@ -10957,6 +12145,8 @@
       <c r="H188" t="n">
         <v>50.4</v>
       </c>
+      <c r="I188"/>
+      <c r="J188"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -10965,6 +12155,7 @@
       <c r="B189" t="n">
         <v>51.3818</v>
       </c>
+      <c r="C189"/>
       <c r="D189" t="n">
         <v>51.8</v>
       </c>
@@ -10980,6 +12171,8 @@
       <c r="H189" t="n">
         <v>51.3</v>
       </c>
+      <c r="I189"/>
+      <c r="J189"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -10988,6 +12181,7 @@
       <c r="B190" t="n">
         <v>51.1031</v>
       </c>
+      <c r="C190"/>
       <c r="D190" t="n">
         <v>51.1</v>
       </c>
@@ -11003,6 +12197,8 @@
       <c r="H190" t="n">
         <v>50.8</v>
       </c>
+      <c r="I190"/>
+      <c r="J190"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -11011,6 +12207,7 @@
       <c r="B191" t="n">
         <v>51.298</v>
       </c>
+      <c r="C191"/>
       <c r="D191" t="n">
         <v>51.7</v>
       </c>
@@ -11026,6 +12223,8 @@
       <c r="H191" t="n">
         <v>50.7</v>
       </c>
+      <c r="I191"/>
+      <c r="J191"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -11034,6 +12233,7 @@
       <c r="B192" t="n">
         <v>51.6204</v>
       </c>
+      <c r="C192"/>
       <c r="D192" t="n">
         <v>52.7</v>
       </c>
@@ -11049,6 +12249,8 @@
       <c r="H192" t="n">
         <v>51.4</v>
       </c>
+      <c r="I192"/>
+      <c r="J192"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -11057,6 +12259,7 @@
       <c r="B193" t="n">
         <v>52.6848</v>
       </c>
+      <c r="C193"/>
       <c r="D193" t="n">
         <v>54.3</v>
       </c>
@@ -11072,6 +12275,8 @@
       <c r="H193" t="n">
         <v>53.3</v>
       </c>
+      <c r="I193"/>
+      <c r="J193"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -11080,6 +12285,7 @@
       <c r="B194" t="n">
         <v>54.005</v>
       </c>
+      <c r="C194"/>
       <c r="D194" t="n">
         <v>56.5</v>
       </c>
@@ -11095,6 +12301,8 @@
       <c r="H194" t="n">
         <v>53.1</v>
       </c>
+      <c r="I194"/>
+      <c r="J194"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
@@ -11103,6 +12311,7 @@
       <c r="B195" t="n">
         <v>53.1737</v>
       </c>
+      <c r="C195"/>
       <c r="D195" t="n">
         <v>54.8</v>
       </c>
@@ -11118,6 +12327,8 @@
       <c r="H195" t="n">
         <v>52.3</v>
       </c>
+      <c r="I195"/>
+      <c r="J195"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -11126,6 +12337,7 @@
       <c r="B196" t="n">
         <v>53.0302</v>
       </c>
+      <c r="C196"/>
       <c r="D196" t="n">
         <v>53.7</v>
       </c>
@@ -11141,6 +12353,8 @@
       <c r="H196" t="n">
         <v>52.4</v>
       </c>
+      <c r="I196"/>
+      <c r="J196"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -11149,6 +12363,7 @@
       <c r="B197" t="n">
         <v>53.3597</v>
       </c>
+      <c r="C197"/>
       <c r="D197" t="n">
         <v>54.1</v>
       </c>
@@ -11164,6 +12379,8 @@
       <c r="H197" t="n">
         <v>54</v>
       </c>
+      <c r="I197"/>
+      <c r="J197"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -11172,6 +12389,7 @@
       <c r="B198" t="n">
         <v>52.1706</v>
       </c>
+      <c r="C198"/>
       <c r="D198" t="n">
         <v>52.3</v>
       </c>
@@ -11187,6 +12405,8 @@
       <c r="H198" t="n">
         <v>53.2</v>
       </c>
+      <c r="I198"/>
+      <c r="J198"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
@@ -11195,6 +12415,7 @@
       <c r="B199" t="n">
         <v>51.7868</v>
       </c>
+      <c r="C199"/>
       <c r="D199" t="n">
         <v>52</v>
       </c>
@@ -11210,6 +12431,8 @@
       <c r="H199" t="n">
         <v>52.6</v>
       </c>
+      <c r="I199"/>
+      <c r="J199"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -11218,6 +12441,7 @@
       <c r="B200" t="n">
         <v>51.7759</v>
       </c>
+      <c r="C200"/>
       <c r="D200" t="n">
         <v>52.4</v>
       </c>
@@ -11233,6 +12457,8 @@
       <c r="H200" t="n">
         <v>51.9</v>
       </c>
+      <c r="I200"/>
+      <c r="J200"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -11241,6 +12467,7 @@
       <c r="B201" t="n">
         <v>50.6851</v>
       </c>
+      <c r="C201"/>
       <c r="D201" t="n">
         <v>51.4</v>
       </c>
@@ -11256,6 +12483,8 @@
       <c r="H201" t="n">
         <v>49.8</v>
       </c>
+      <c r="I201"/>
+      <c r="J201"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -11264,6 +12493,7 @@
       <c r="B202" t="n">
         <v>50.3273</v>
       </c>
+      <c r="C202"/>
       <c r="D202" t="n">
         <v>49.9</v>
       </c>
@@ -11279,6 +12509,8 @@
       <c r="H202" t="n">
         <v>50.7</v>
       </c>
+      <c r="I202"/>
+      <c r="J202"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -11287,6 +12519,7 @@
       <c r="B203" t="n">
         <v>50.636</v>
       </c>
+      <c r="C203"/>
       <c r="D203" t="n">
         <v>51.4</v>
       </c>
@@ -11302,6 +12535,8 @@
       <c r="H203" t="n">
         <v>49</v>
       </c>
+      <c r="I203"/>
+      <c r="J203"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
@@ -11310,6 +12545,7 @@
       <c r="B204" t="n">
         <v>50.0939</v>
       </c>
+      <c r="C204"/>
       <c r="D204" t="n">
         <v>49.5</v>
       </c>
@@ -11325,6 +12561,8 @@
       <c r="H204" t="n">
         <v>49</v>
       </c>
+      <c r="I204"/>
+      <c r="J204"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
@@ -11333,6 +12571,7 @@
       <c r="B205" t="n">
         <v>50.5506</v>
       </c>
+      <c r="C205"/>
       <c r="D205" t="n">
         <v>51.2</v>
       </c>
@@ -11348,6 +12587,8 @@
       <c r="H205" t="n">
         <v>48.4</v>
       </c>
+      <c r="I205"/>
+      <c r="J205"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
@@ -11356,6 +12597,7 @@
       <c r="B206" t="n">
         <v>50.9605</v>
       </c>
+      <c r="C206"/>
       <c r="D206" t="n">
         <v>50.9</v>
       </c>
@@ -11371,6 +12613,8 @@
       <c r="H206" t="n">
         <v>49.9</v>
       </c>
+      <c r="I206"/>
+      <c r="J206"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -11379,6 +12623,7 @@
       <c r="B207" t="n">
         <v>51.0488</v>
       </c>
+      <c r="C207"/>
       <c r="D207" t="n">
         <v>51.1</v>
       </c>
@@ -11394,6 +12639,8 @@
       <c r="H207" t="n">
         <v>51.9</v>
       </c>
+      <c r="I207"/>
+      <c r="J207"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -11402,6 +12649,7 @@
       <c r="B208" t="n">
         <v>52.1977</v>
       </c>
+      <c r="C208"/>
       <c r="D208" t="n">
         <v>52.8</v>
       </c>
@@ -11417,6 +12665,8 @@
       <c r="H208" t="n">
         <v>53.3</v>
       </c>
+      <c r="I208"/>
+      <c r="J208"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -11425,6 +12675,7 @@
       <c r="B209" t="n">
         <v>52.0146</v>
       </c>
+      <c r="C209"/>
       <c r="D209" t="n">
         <v>52.1</v>
       </c>
@@ -11440,6 +12691,8 @@
       <c r="H209" t="n">
         <v>53.8</v>
       </c>
+      <c r="I209"/>
+      <c r="J209"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -11448,6 +12701,7 @@
       <c r="B210" t="n">
         <v>52.2487</v>
       </c>
+      <c r="C210"/>
       <c r="D210" t="n">
         <v>51.1</v>
       </c>
@@ -11463,6 +12717,8 @@
       <c r="H210" t="n">
         <v>54.8</v>
       </c>
+      <c r="I210"/>
+      <c r="J210"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
@@ -11471,6 +12727,7 @@
       <c r="B211" t="n">
         <v>52.5429</v>
       </c>
+      <c r="C211"/>
       <c r="D211" t="n">
         <v>51.9</v>
       </c>
@@ -11486,6 +12743,8 @@
       <c r="H211" t="n">
         <v>54.1</v>
       </c>
+      <c r="I211"/>
+      <c r="J211"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
@@ -11494,6 +12753,7 @@
       <c r="B212" t="n">
         <v>52.395</v>
       </c>
+      <c r="C212"/>
       <c r="D212" t="n">
         <v>51.8</v>
       </c>
@@ -11509,6 +12769,8 @@
       <c r="H212" t="n">
         <v>55.3</v>
       </c>
+      <c r="I212"/>
+      <c r="J212"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
@@ -11517,6 +12779,7 @@
       <c r="B213" t="n">
         <v>52.3336</v>
       </c>
+      <c r="C213"/>
       <c r="D213" t="n">
         <v>53.3</v>
       </c>
@@ -11532,6 +12795,8 @@
       <c r="H213" t="n">
         <v>53.8</v>
       </c>
+      <c r="I213"/>
+      <c r="J213"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n">
@@ -11540,6 +12805,7 @@
       <c r="B214" t="n">
         <v>52.0306</v>
       </c>
+      <c r="C214"/>
       <c r="D214" t="n">
         <v>52.3</v>
       </c>
@@ -11555,6 +12821,8 @@
       <c r="H214" t="n">
         <v>52.7</v>
       </c>
+      <c r="I214"/>
+      <c r="J214"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n">
@@ -11563,6 +12831,7 @@
       <c r="B215" t="n">
         <v>52.2655</v>
       </c>
+      <c r="C215"/>
       <c r="D215" t="n">
         <v>52.1</v>
       </c>
@@ -11578,6 +12847,8 @@
       <c r="H215" t="n">
         <v>54.1</v>
       </c>
+      <c r="I215"/>
+      <c r="J215"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
@@ -11586,6 +12857,7 @@
       <c r="B216" t="n">
         <v>52.8291</v>
       </c>
+      <c r="C216"/>
       <c r="D216" t="n">
         <v>52.9</v>
       </c>
@@ -11601,6 +12873,8 @@
       <c r="H216" t="n">
         <v>54.9</v>
       </c>
+      <c r="I216"/>
+      <c r="J216"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n">
@@ -11609,6 +12883,7 @@
       <c r="B217" t="n">
         <v>53.1925</v>
       </c>
+      <c r="C217"/>
       <c r="D217" t="n">
         <v>53.2</v>
       </c>
@@ -11624,6 +12899,8 @@
       <c r="H217" t="n">
         <v>55.6</v>
       </c>
+      <c r="I217"/>
+      <c r="J217"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
@@ -11632,6 +12909,7 @@
       <c r="B218" t="n">
         <v>52.3395</v>
       </c>
+      <c r="C218"/>
       <c r="D218" t="n">
         <v>52.3</v>
       </c>
@@ -11647,6 +12925,8 @@
       <c r="H218" t="n">
         <v>53.2</v>
       </c>
+      <c r="I218"/>
+      <c r="J218"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
@@ -11655,6 +12935,7 @@
       <c r="B219" t="n">
         <v>51.2343</v>
       </c>
+      <c r="C219"/>
       <c r="D219" t="n">
         <v>50.5</v>
       </c>
@@ -11670,6 +12951,8 @@
       <c r="H219" t="n">
         <v>52.2</v>
       </c>
+      <c r="I219"/>
+      <c r="J219"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n">
@@ -11678,6 +12961,7 @@
       <c r="B220" t="n">
         <v>51.5727</v>
       </c>
+      <c r="C220"/>
       <c r="D220" t="n">
         <v>50.7</v>
       </c>
@@ -11693,6 +12977,8 @@
       <c r="H220" t="n">
         <v>53.5</v>
       </c>
+      <c r="I220"/>
+      <c r="J220"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
@@ -11701,6 +12987,7 @@
       <c r="B221" t="n">
         <v>51.7106</v>
       </c>
+      <c r="C221"/>
       <c r="D221" t="n">
         <v>51.8</v>
       </c>
@@ -11716,6 +13003,8 @@
       <c r="H221" t="n">
         <v>53.9</v>
       </c>
+      <c r="I221"/>
+      <c r="J221"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
@@ -11724,6 +13013,7 @@
       <c r="B222" t="n">
         <v>51.4601</v>
       </c>
+      <c r="C222"/>
       <c r="D222" t="n">
         <v>52.1</v>
       </c>
@@ -11739,6 +13029,8 @@
       <c r="H222" t="n">
         <v>52.4</v>
       </c>
+      <c r="I222"/>
+      <c r="J222"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n">
@@ -11747,6 +13039,7 @@
       <c r="B223" t="n">
         <v>52.8176</v>
       </c>
+      <c r="C223"/>
       <c r="D223" t="n">
         <v>54.5</v>
       </c>
@@ -11762,6 +13055,8 @@
       <c r="H223" t="n">
         <v>53.5</v>
       </c>
+      <c r="I223"/>
+      <c r="J223"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
@@ -11770,6 +13065,7 @@
       <c r="B224" t="n">
         <v>52.0172</v>
       </c>
+      <c r="C224"/>
       <c r="D224" t="n">
         <v>53.8</v>
       </c>
@@ -11785,6 +13081,8 @@
       <c r="H224" t="n">
         <v>51.2</v>
       </c>
+      <c r="I224"/>
+      <c r="J224"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
@@ -11793,6 +13091,7 @@
       <c r="B225" t="n">
         <v>51.6875</v>
       </c>
+      <c r="C225"/>
       <c r="D225" t="n">
         <v>53.6</v>
       </c>
@@ -11808,6 +13107,8 @@
       <c r="H225" t="n">
         <v>49.8</v>
       </c>
+      <c r="I225"/>
+      <c r="J225"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
@@ -11816,6 +13117,7 @@
       <c r="B226" t="n">
         <v>52.5872</v>
       </c>
+      <c r="C226"/>
       <c r="D226" t="n">
         <v>54.3</v>
       </c>
@@ -11831,6 +13133,8 @@
       <c r="H226" t="n">
         <v>51</v>
       </c>
+      <c r="I226"/>
+      <c r="J226"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
@@ -11839,6 +13143,7 @@
       <c r="B227" t="n">
         <v>53.4698</v>
       </c>
+      <c r="C227"/>
       <c r="D227" t="n">
         <v>55</v>
       </c>
@@ -11854,6 +13159,8 @@
       <c r="H227" t="n">
         <v>50.9</v>
       </c>
+      <c r="I227"/>
+      <c r="J227"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
@@ -11862,6 +13169,7 @@
       <c r="B228" t="n">
         <v>53.6725</v>
       </c>
+      <c r="C228"/>
       <c r="D228" t="n">
         <v>54.3</v>
       </c>
@@ -11877,6 +13185,8 @@
       <c r="H228" t="n">
         <v>52.2</v>
       </c>
+      <c r="I228"/>
+      <c r="J228"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
@@ -11885,6 +13195,7 @@
       <c r="B229" t="n">
         <v>54.8767</v>
       </c>
+      <c r="C229"/>
       <c r="D229" t="n">
         <v>55.6</v>
       </c>
@@ -11900,6 +13211,8 @@
       <c r="H229" t="n">
         <v>53.2</v>
       </c>
+      <c r="I229"/>
+      <c r="J229"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
@@ -11908,6 +13221,7 @@
       <c r="B230" t="n">
         <v>55.2438</v>
       </c>
+      <c r="C230"/>
       <c r="D230" t="n">
         <v>56.4</v>
       </c>
@@ -11923,6 +13237,8 @@
       <c r="H230" t="n">
         <v>53</v>
       </c>
+      <c r="I230"/>
+      <c r="J230"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
@@ -11931,6 +13247,7 @@
       <c r="B231" t="n">
         <v>55.418</v>
       </c>
+      <c r="C231"/>
       <c r="D231" t="n">
         <v>56.8</v>
       </c>
@@ -11946,6 +13263,8 @@
       <c r="H231" t="n">
         <v>55</v>
       </c>
+      <c r="I231"/>
+      <c r="J231"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n">
@@ -11954,6 +13273,7 @@
       <c r="B232" t="n">
         <v>56.2358</v>
       </c>
+      <c r="C232"/>
       <c r="D232" t="n">
         <v>58.3</v>
       </c>
@@ -11969,6 +13289,8 @@
       <c r="H232" t="n">
         <v>55.7</v>
       </c>
+      <c r="I232"/>
+      <c r="J232"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n">
@@ -11977,6 +13299,7 @@
       <c r="B233" t="n">
         <v>56.7381</v>
       </c>
+      <c r="C233"/>
       <c r="D233" t="n">
         <v>58.2</v>
       </c>
@@ -11992,6 +13315,8 @@
       <c r="H233" t="n">
         <v>56.2</v>
       </c>
+      <c r="I233"/>
+      <c r="J233"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
@@ -12000,6 +13325,7 @@
       <c r="B234" t="n">
         <v>57.0241</v>
       </c>
+      <c r="C234"/>
       <c r="D234" t="n">
         <v>59.5</v>
       </c>
@@ -12015,6 +13341,8 @@
       <c r="H234" t="n">
         <v>55.1</v>
       </c>
+      <c r="I234"/>
+      <c r="J234"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n">
@@ -12023,6 +13351,7 @@
       <c r="B235" t="n">
         <v>57.3512</v>
       </c>
+      <c r="C235"/>
       <c r="D235" t="n">
         <v>59.6</v>
       </c>
@@ -12038,6 +13367,8 @@
       <c r="H235" t="n">
         <v>55.2</v>
       </c>
+      <c r="I235"/>
+      <c r="J235"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n">
@@ -12046,6 +13377,7 @@
       <c r="B236" t="n">
         <v>56.5873</v>
       </c>
+      <c r="C236"/>
       <c r="D236" t="n">
         <v>58.1</v>
       </c>
@@ -12061,6 +13393,8 @@
       <c r="H236" t="n">
         <v>55.1</v>
       </c>
+      <c r="I236"/>
+      <c r="J236"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
@@ -12069,6 +13403,7 @@
       <c r="B237" t="n">
         <v>57.4297</v>
       </c>
+      <c r="C237"/>
       <c r="D237" t="n">
         <v>59.3</v>
       </c>
@@ -12084,6 +13419,8 @@
       <c r="H237" t="n">
         <v>56.3</v>
       </c>
+      <c r="I237"/>
+      <c r="J237"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
@@ -12092,6 +13429,7 @@
       <c r="B238" t="n">
         <v>58.1415</v>
       </c>
+      <c r="C238"/>
       <c r="D238" t="n">
         <v>60.6</v>
       </c>
@@ -12107,6 +13445,8 @@
       <c r="H238" t="n">
         <v>56.3</v>
       </c>
+      <c r="I238"/>
+      <c r="J238"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n">
@@ -12115,6 +13455,7 @@
       <c r="B239" t="n">
         <v>58.511</v>
       </c>
+      <c r="C239"/>
       <c r="D239" t="n">
         <v>60.6</v>
       </c>
@@ -12130,6 +13471,8 @@
       <c r="H239" t="n">
         <v>57.8</v>
       </c>
+      <c r="I239"/>
+      <c r="J239"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
@@ -12138,6 +13481,7 @@
       <c r="B240" t="n">
         <v>60.0707</v>
       </c>
+      <c r="C240"/>
       <c r="D240" t="n">
         <v>62.5</v>
       </c>
@@ -12153,6 +13497,8 @@
       <c r="H240" t="n">
         <v>58.3</v>
       </c>
+      <c r="I240"/>
+      <c r="J240"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n">
@@ -12161,6 +13507,7 @@
       <c r="B241" t="n">
         <v>60.5791</v>
       </c>
+      <c r="C241"/>
       <c r="D241" t="n">
         <v>63.3</v>
       </c>
@@ -12176,6 +13523,8 @@
       <c r="H241" t="n">
         <v>57.4</v>
       </c>
+      <c r="I241"/>
+      <c r="J241"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n">
@@ -12184,6 +13533,7 @@
       <c r="B242" t="n">
         <v>59.5783</v>
       </c>
+      <c r="C242"/>
       <c r="D242" t="n">
         <v>61.1</v>
       </c>
@@ -12199,6 +13549,8 @@
       <c r="H242" t="n">
         <v>59</v>
       </c>
+      <c r="I242"/>
+      <c r="J242"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n">
@@ -12207,6 +13559,7 @@
       <c r="B243" t="n">
         <v>58.5821</v>
       </c>
+      <c r="C243"/>
       <c r="D243" t="n">
         <v>60.6</v>
       </c>
@@ -12222,6 +13575,8 @@
       <c r="H243" t="n">
         <v>56.8</v>
       </c>
+      <c r="I243"/>
+      <c r="J243"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n">
@@ -12230,6 +13585,7 @@
       <c r="B244" t="n">
         <v>56.5574</v>
       </c>
+      <c r="C244"/>
       <c r="D244" t="n">
         <v>58.2</v>
       </c>
@@ -12245,6 +13601,8 @@
       <c r="H244" t="n">
         <v>55.1</v>
       </c>
+      <c r="I244"/>
+      <c r="J244"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n">
@@ -12253,6 +13611,7 @@
       <c r="B245" t="n">
         <v>56.235</v>
       </c>
+      <c r="C245"/>
       <c r="D245" t="n">
         <v>58.1</v>
       </c>
@@ -12268,6 +13627,8 @@
       <c r="H245" t="n">
         <v>53.5</v>
       </c>
+      <c r="I245"/>
+      <c r="J245"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n">
@@ -12276,6 +13637,7 @@
       <c r="B246" t="n">
         <v>55.5483</v>
       </c>
+      <c r="C246"/>
       <c r="D246" t="n">
         <v>56.9</v>
       </c>
@@ -12291,6 +13653,8 @@
       <c r="H246" t="n">
         <v>52.7</v>
       </c>
+      <c r="I246"/>
+      <c r="J246"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n">
@@ -12299,6 +13663,7 @@
       <c r="B247" t="n">
         <v>54.9486</v>
       </c>
+      <c r="C247"/>
       <c r="D247" t="n">
         <v>55.9</v>
       </c>
@@ -12314,6 +13679,8 @@
       <c r="H247" t="n">
         <v>53.3</v>
       </c>
+      <c r="I247"/>
+      <c r="J247"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n">
@@ -12322,6 +13689,7 @@
       <c r="B248" t="n">
         <v>55.0731</v>
       </c>
+      <c r="C248"/>
       <c r="D248" t="n">
         <v>56.9</v>
       </c>
@@ -12337,6 +13705,8 @@
       <c r="H248" t="n">
         <v>51.5</v>
       </c>
+      <c r="I248"/>
+      <c r="J248"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n">
@@ -12345,6 +13715,7 @@
       <c r="B249" t="n">
         <v>54.5531</v>
       </c>
+      <c r="C249"/>
       <c r="D249" t="n">
         <v>55.9</v>
       </c>
@@ -12360,6 +13731,8 @@
       <c r="H249" t="n">
         <v>50.1</v>
       </c>
+      <c r="I249"/>
+      <c r="J249"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n">
@@ -12368,6 +13741,7 @@
       <c r="B250" t="n">
         <v>53.174</v>
       </c>
+      <c r="C250"/>
       <c r="D250" t="n">
         <v>53.7</v>
       </c>
@@ -12383,6 +13757,8 @@
       <c r="H250" t="n">
         <v>50</v>
       </c>
+      <c r="I250"/>
+      <c r="J250"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n">
@@ -12391,6 +13767,7 @@
       <c r="B251" t="n">
         <v>51.9661</v>
       </c>
+      <c r="C251"/>
       <c r="D251" t="n">
         <v>52.2</v>
       </c>
@@ -12406,6 +13783,8 @@
       <c r="H251" t="n">
         <v>49.2</v>
       </c>
+      <c r="I251"/>
+      <c r="J251"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n">
@@ -12414,6 +13793,7 @@
       <c r="B252" t="n">
         <v>51.7753</v>
       </c>
+      <c r="C252"/>
       <c r="D252" t="n">
         <v>51.8</v>
       </c>
@@ -12429,6 +13809,8 @@
       <c r="H252" t="n">
         <v>48.6</v>
       </c>
+      <c r="I252"/>
+      <c r="J252"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n">
@@ -12437,6 +13819,7 @@
       <c r="B253" t="n">
         <v>51.3891</v>
       </c>
+      <c r="C253"/>
       <c r="D253" t="n">
         <v>51.5</v>
       </c>
@@ -12452,6 +13835,8 @@
       <c r="H253" t="n">
         <v>49.2</v>
       </c>
+      <c r="I253"/>
+      <c r="J253"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n">
@@ -12460,6 +13845,7 @@
       <c r="B254" t="n">
         <v>50.5</v>
       </c>
+      <c r="C254"/>
       <c r="D254" t="n">
         <v>49.7</v>
       </c>
@@ -12475,6 +13861,8 @@
       <c r="H254" t="n">
         <v>47.8</v>
       </c>
+      <c r="I254"/>
+      <c r="J254"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n">
@@ -12483,6 +13871,7 @@
       <c r="B255" t="n">
         <v>49.3</v>
       </c>
+      <c r="C255"/>
       <c r="D255" t="n">
         <v>47.6</v>
       </c>
@@ -12498,6 +13887,8 @@
       <c r="H255" t="n">
         <v>47.7</v>
       </c>
+      <c r="I255"/>
+      <c r="J255"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n">
@@ -12506,6 +13897,7 @@
       <c r="B256" t="n">
         <v>47.5</v>
       </c>
+      <c r="C256"/>
       <c r="D256" t="n">
         <v>44.1</v>
       </c>
@@ -12521,6 +13913,8 @@
       <c r="H256" t="n">
         <v>47.4</v>
       </c>
+      <c r="I256"/>
+      <c r="J256"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n">
@@ -12529,6 +13923,7 @@
       <c r="B257" t="n">
         <v>47.9</v>
       </c>
+      <c r="C257"/>
       <c r="D257" t="n">
         <v>44.4</v>
       </c>
@@ -12544,6 +13939,8 @@
       <c r="H257" t="n">
         <v>49.1</v>
       </c>
+      <c r="I257"/>
+      <c r="J257"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n">
@@ -12552,6 +13949,7 @@
       <c r="B258" t="n">
         <v>47.7</v>
       </c>
+      <c r="C258"/>
       <c r="D258" t="n">
         <v>44.3</v>
       </c>
@@ -12567,6 +13965,8 @@
       <c r="H258" t="n">
         <v>49.7</v>
       </c>
+      <c r="I258"/>
+      <c r="J258"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n">
@@ -12575,6 +13975,7 @@
       <c r="B259" t="n">
         <v>47.6</v>
       </c>
+      <c r="C259"/>
       <c r="D259" t="n">
         <v>45</v>
       </c>
@@ -12590,6 +13991,8 @@
       <c r="H259" t="n">
         <v>48.4</v>
       </c>
+      <c r="I259"/>
+      <c r="J259"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n">
@@ -12598,6 +14001,7 @@
       <c r="B260" t="n">
         <v>46.5</v>
       </c>
+      <c r="C260"/>
       <c r="D260" t="n">
         <v>43.2</v>
       </c>
@@ -12613,6 +14017,8 @@
       <c r="H260" t="n">
         <v>48.5</v>
       </c>
+      <c r="I260"/>
+      <c r="J260"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n">
@@ -12621,6 +14027,7 @@
       <c r="B261" t="n">
         <v>47</v>
       </c>
+      <c r="C261"/>
       <c r="D261" t="n">
         <v>43.5</v>
       </c>
@@ -12636,6 +14043,8 @@
       <c r="H261" t="n">
         <v>48.7</v>
       </c>
+      <c r="I261"/>
+      <c r="J261"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n">
@@ -12644,6 +14053,7 @@
       <c r="B262" t="n">
         <v>45.7</v>
       </c>
+      <c r="C262"/>
       <c r="D262" t="n">
         <v>41.7</v>
       </c>
@@ -12659,6 +14069,8 @@
       <c r="H262" t="n">
         <v>47.8</v>
       </c>
+      <c r="I262"/>
+      <c r="J262"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n">
@@ -12667,6 +14079,7 @@
       <c r="B263" t="n">
         <v>45.9</v>
       </c>
+      <c r="C263"/>
       <c r="D263" t="n">
         <v>42.1</v>
       </c>
@@ -12682,6 +14095,8 @@
       <c r="H263" t="n">
         <v>47.7</v>
       </c>
+      <c r="I263"/>
+      <c r="J263"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n">
@@ -12690,6 +14105,7 @@
       <c r="B264" t="n">
         <v>46.9</v>
       </c>
+      <c r="C264"/>
       <c r="D264" t="n">
         <v>44.1</v>
       </c>
@@ -12705,6 +14121,8 @@
       <c r="H264" t="n">
         <v>47.6</v>
       </c>
+      <c r="I264"/>
+      <c r="J264"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n">
@@ -12713,6 +14131,7 @@
       <c r="B265" t="n">
         <v>46.3</v>
       </c>
+      <c r="C265"/>
       <c r="D265" t="n">
         <v>43.7</v>
       </c>
@@ -12728,6 +14147,8 @@
       <c r="H265" t="n">
         <v>46.2</v>
       </c>
+      <c r="I265"/>
+      <c r="J265"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n">
@@ -12736,6 +14157,7 @@
       <c r="B266" t="n">
         <v>47.9</v>
       </c>
+      <c r="C266"/>
       <c r="D266" t="n">
         <v>45.3</v>
       </c>
@@ -12751,6 +14173,8 @@
       <c r="H266" t="n">
         <v>48.9</v>
       </c>
+      <c r="I266"/>
+      <c r="J266"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n">
@@ -12759,6 +14183,7 @@
       <c r="B267" t="n">
         <v>49.2</v>
       </c>
+      <c r="C267"/>
       <c r="D267" t="n">
         <v>48</v>
       </c>
@@ -12774,6 +14199,8 @@
       <c r="H267" t="n">
         <v>48.7</v>
       </c>
+      <c r="I267"/>
+      <c r="J267"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n">
@@ -12782,6 +14209,7 @@
       <c r="B268" t="n">
         <v>44.5</v>
       </c>
+      <c r="C268"/>
       <c r="D268" t="n">
         <v>45.4</v>
       </c>
@@ -12797,6 +14225,8 @@
       <c r="H268" t="n">
         <v>40.3</v>
       </c>
+      <c r="I268"/>
+      <c r="J268"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n">
@@ -12805,6 +14235,7 @@
       <c r="B269" t="n">
         <v>33.4</v>
       </c>
+      <c r="C269"/>
       <c r="D269" t="n">
         <v>34.5</v>
       </c>
@@ -12820,6 +14251,8 @@
       <c r="H269" t="n">
         <v>31.1</v>
       </c>
+      <c r="I269"/>
+      <c r="J269"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n">
@@ -12828,6 +14261,7 @@
       <c r="B270" t="n">
         <v>39.4</v>
       </c>
+      <c r="C270"/>
       <c r="D270" t="n">
         <v>36.6</v>
       </c>
@@ -12843,6 +14277,8 @@
       <c r="H270" t="n">
         <v>45.4</v>
       </c>
+      <c r="I270"/>
+      <c r="J270"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n">
@@ -12851,6 +14287,7 @@
       <c r="B271" t="n">
         <v>47.4</v>
       </c>
+      <c r="C271"/>
       <c r="D271" t="n">
         <v>45.2</v>
       </c>
@@ -12866,6 +14303,8 @@
       <c r="H271" t="n">
         <v>47.5</v>
       </c>
+      <c r="I271"/>
+      <c r="J271"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n">
@@ -12874,6 +14313,7 @@
       <c r="B272" t="n">
         <v>51.8</v>
       </c>
+      <c r="C272"/>
       <c r="D272" t="n">
         <v>51</v>
       </c>
@@ -12889,6 +14329,8 @@
       <c r="H272" t="n">
         <v>51.9</v>
       </c>
+      <c r="I272"/>
+      <c r="J272"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n">
@@ -12897,6 +14339,7 @@
       <c r="B273" t="n">
         <v>51.7</v>
       </c>
+      <c r="C273"/>
       <c r="D273" t="n">
         <v>52.2</v>
       </c>
@@ -12912,6 +14355,8 @@
       <c r="H273" t="n">
         <v>53.1</v>
       </c>
+      <c r="I273"/>
+      <c r="J273"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n">
@@ -12920,6 +14365,7 @@
       <c r="B274" t="n">
         <v>53.7</v>
       </c>
+      <c r="C274"/>
       <c r="D274" t="n">
         <v>56.4</v>
       </c>
@@ -12935,6 +14381,8 @@
       <c r="H274" t="n">
         <v>53.2</v>
       </c>
+      <c r="I274"/>
+      <c r="J274"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n">
@@ -12943,6 +14391,7 @@
       <c r="B275" t="n">
         <v>54.8</v>
       </c>
+      <c r="C275"/>
       <c r="D275" t="n">
         <v>58.2</v>
       </c>
@@ -12958,6 +14407,8 @@
       <c r="H275" t="n">
         <v>53.8</v>
       </c>
+      <c r="I275"/>
+      <c r="J275"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n">
@@ -12966,6 +14417,7 @@
       <c r="B276" t="n">
         <v>53.8</v>
       </c>
+      <c r="C276"/>
       <c r="D276" t="n">
         <v>57.8</v>
       </c>
@@ -12981,6 +14433,8 @@
       <c r="H276" t="n">
         <v>51.5</v>
       </c>
+      <c r="I276"/>
+      <c r="J276"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n">
@@ -12989,6 +14443,7 @@
       <c r="B277" t="n">
         <v>55.5</v>
       </c>
+      <c r="C277"/>
       <c r="D277" t="n">
         <v>58.6</v>
       </c>
@@ -13004,6 +14459,8 @@
       <c r="H277" t="n">
         <v>53.5</v>
       </c>
+      <c r="I277"/>
+      <c r="J277"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n">
@@ -13012,6 +14469,7 @@
       <c r="B278" t="n">
         <v>54.7</v>
       </c>
+      <c r="C278"/>
       <c r="D278" t="n">
         <v>57</v>
       </c>
@@ -13027,6 +14485,8 @@
       <c r="H278" t="n">
         <v>52.4</v>
       </c>
+      <c r="I278"/>
+      <c r="J278"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n">
@@ -13035,6 +14495,7 @@
       <c r="B279" t="n">
         <v>57.7</v>
       </c>
+      <c r="C279"/>
       <c r="D279" t="n">
         <v>60.6</v>
       </c>
@@ -13050,6 +14511,8 @@
       <c r="H279" t="n">
         <v>56.8</v>
       </c>
+      <c r="I279"/>
+      <c r="J279"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n">
@@ -13058,6 +14521,7 @@
       <c r="B280" t="n">
         <v>62.5</v>
       </c>
+      <c r="C280"/>
       <c r="D280" t="n">
         <v>66.6</v>
       </c>
@@ -13073,6 +14537,8 @@
       <c r="H280" t="n">
         <v>59.8</v>
       </c>
+      <c r="I280"/>
+      <c r="J280"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n">
@@ -13081,6 +14547,7 @@
       <c r="B281" t="n">
         <v>62.9</v>
       </c>
+      <c r="C281"/>
       <c r="D281" t="n">
         <v>66.2</v>
       </c>
@@ -13096,6 +14563,8 @@
       <c r="H281" t="n">
         <v>60.7</v>
       </c>
+      <c r="I281"/>
+      <c r="J281"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n">
@@ -13104,6 +14573,7 @@
       <c r="B282" t="n">
         <v>63.1</v>
       </c>
+      <c r="C282"/>
       <c r="D282" t="n">
         <v>64.4</v>
       </c>
@@ -13119,6 +14589,8 @@
       <c r="H282" t="n">
         <v>62.3</v>
       </c>
+      <c r="I282"/>
+      <c r="J282"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n">
@@ -13127,6 +14599,7 @@
       <c r="B283" t="n">
         <v>63.4</v>
       </c>
+      <c r="C283"/>
       <c r="D283" t="n">
         <v>65.1</v>
       </c>
@@ -13142,6 +14615,8 @@
       <c r="H283" t="n">
         <v>62.2</v>
       </c>
+      <c r="I283"/>
+      <c r="J283"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n">
@@ -13150,6 +14625,7 @@
       <c r="B284" t="n">
         <v>62.8</v>
       </c>
+      <c r="C284"/>
       <c r="D284" t="n">
         <v>65.9</v>
       </c>
@@ -13165,6 +14641,8 @@
       <c r="H284" t="n">
         <v>60.3</v>
       </c>
+      <c r="I284"/>
+      <c r="J284"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n">
@@ -13173,6 +14651,7 @@
       <c r="B285" t="n">
         <v>61.4</v>
       </c>
+      <c r="C285"/>
       <c r="D285" t="n">
         <v>62.6</v>
       </c>
@@ -13188,6 +14667,8 @@
       <c r="H285" t="n">
         <v>60.9</v>
       </c>
+      <c r="I285"/>
+      <c r="J285"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n">
@@ -13196,6 +14677,7 @@
       <c r="B286" t="n">
         <v>58.6</v>
       </c>
+      <c r="C286"/>
       <c r="D286" t="n">
         <v>58.4</v>
       </c>
@@ -13211,6 +14693,8 @@
       <c r="H286" t="n">
         <v>59.7</v>
       </c>
+      <c r="I286"/>
+      <c r="J286"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n">
@@ -13219,6 +14703,7 @@
       <c r="B287" t="n">
         <v>58.3</v>
       </c>
+      <c r="C287"/>
       <c r="D287" t="n">
         <v>57.8</v>
       </c>
@@ -13234,6 +14719,8 @@
       <c r="H287" t="n">
         <v>61.1</v>
       </c>
+      <c r="I287"/>
+      <c r="J287"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n">
@@ -13242,6 +14729,7 @@
       <c r="B288" t="n">
         <v>58.4</v>
       </c>
+      <c r="C288"/>
       <c r="D288" t="n">
         <v>57.4</v>
       </c>
@@ -13257,6 +14745,8 @@
       <c r="H288" t="n">
         <v>62.8</v>
       </c>
+      <c r="I288"/>
+      <c r="J288"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n">
@@ -13265,6 +14755,7 @@
       <c r="B289" t="n">
         <v>58</v>
       </c>
+      <c r="C289"/>
       <c r="D289" t="n">
         <v>57.4</v>
       </c>
@@ -13280,6 +14771,8 @@
       <c r="H289" t="n">
         <v>62</v>
       </c>
+      <c r="I289"/>
+      <c r="J289"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n">
@@ -13288,6 +14781,7 @@
       <c r="B290" t="n">
         <v>58.7</v>
       </c>
+      <c r="C290"/>
       <c r="D290" t="n">
         <v>59.8</v>
       </c>
@@ -13303,6 +14797,8 @@
       <c r="H290" t="n">
         <v>58.3</v>
       </c>
+      <c r="I290"/>
+      <c r="J290"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n">
@@ -13311,6 +14807,7 @@
       <c r="B291" t="n">
         <v>58.2</v>
       </c>
+      <c r="C291"/>
       <c r="D291" t="n">
         <v>58.4</v>
       </c>
@@ -13326,6 +14823,8 @@
       <c r="H291" t="n">
         <v>58.3</v>
       </c>
+      <c r="I291"/>
+      <c r="J291"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n">
@@ -13334,6 +14833,7 @@
       <c r="B292" t="n">
         <v>56.5</v>
       </c>
+      <c r="C292"/>
       <c r="D292" t="n">
         <v>56.9</v>
       </c>
@@ -13349,6 +14849,8 @@
       <c r="H292" t="n">
         <v>55.8</v>
       </c>
+      <c r="I292"/>
+      <c r="J292"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n">
@@ -13357,6 +14859,7 @@
       <c r="B293" t="n">
         <v>55.5</v>
       </c>
+      <c r="C293"/>
       <c r="D293" t="n">
         <v>54.6</v>
       </c>
@@ -13372,6 +14875,8 @@
       <c r="H293" t="n">
         <v>54.5</v>
       </c>
+      <c r="I293"/>
+      <c r="J293"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n">
@@ -13380,6 +14885,7 @@
       <c r="B294" t="n">
         <v>54.6</v>
       </c>
+      <c r="C294"/>
       <c r="D294" t="n">
         <v>54.8</v>
       </c>
@@ -13395,6 +14901,8 @@
       <c r="H294" t="n">
         <v>51.9</v>
       </c>
+      <c r="I294"/>
+      <c r="J294"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n">
@@ -13403,6 +14911,7 @@
       <c r="B295" t="n">
         <v>52.1</v>
       </c>
+      <c r="C295"/>
       <c r="D295" t="n">
         <v>52</v>
       </c>
@@ -13418,6 +14927,8 @@
       <c r="H295" t="n">
         <v>50.9</v>
       </c>
+      <c r="I295"/>
+      <c r="J295"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n">
@@ -13426,6 +14937,7 @@
       <c r="B296" t="n">
         <v>49.8</v>
       </c>
+      <c r="C296"/>
       <c r="D296" t="n">
         <v>49.3</v>
       </c>
@@ -13441,6 +14953,8 @@
       <c r="H296" t="n">
         <v>48.5</v>
       </c>
+      <c r="I296"/>
+      <c r="J296"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n">
@@ -13449,6 +14963,7 @@
       <c r="B297" t="n">
         <v>49.6</v>
       </c>
+      <c r="C297"/>
       <c r="D297" t="n">
         <v>49.1</v>
       </c>
@@ -13464,6 +14979,8 @@
       <c r="H297" t="n">
         <v>48</v>
       </c>
+      <c r="I297"/>
+      <c r="J297"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n">
@@ -13472,6 +14989,7 @@
       <c r="B298" t="n">
         <v>48.4</v>
       </c>
+      <c r="C298"/>
       <c r="D298" t="n">
         <v>47.8</v>
       </c>
@@ -13487,6 +15005,8 @@
       <c r="H298" t="n">
         <v>48.3</v>
       </c>
+      <c r="I298"/>
+      <c r="J298"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n">
@@ -13495,6 +15015,7 @@
       <c r="B299" t="n">
         <v>46.4</v>
       </c>
+      <c r="C299"/>
       <c r="D299" t="n">
         <v>45.1</v>
       </c>
@@ -13510,6 +15031,8 @@
       <c r="H299" t="n">
         <v>46.5</v>
       </c>
+      <c r="I299"/>
+      <c r="J299"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n">
@@ -13518,6 +15041,7 @@
       <c r="B300" t="n">
         <v>47.1</v>
       </c>
+      <c r="C300"/>
       <c r="D300" t="n">
         <v>46.2</v>
       </c>
@@ -13533,6 +15057,8 @@
       <c r="H300" t="n">
         <v>48.4</v>
       </c>
+      <c r="I300"/>
+      <c r="J300"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n">
@@ -13541,6 +15067,7 @@
       <c r="B301" t="n">
         <v>47.8</v>
       </c>
+      <c r="C301"/>
       <c r="D301" t="n">
         <v>47.1</v>
       </c>
@@ -13556,6 +15083,8 @@
       <c r="H301" t="n">
         <v>48.5</v>
       </c>
+      <c r="I301"/>
+      <c r="J301"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n">
@@ -13564,6 +15093,7 @@
       <c r="B302" t="n">
         <v>48.8</v>
       </c>
+      <c r="C302"/>
       <c r="D302" t="n">
         <v>47.3</v>
       </c>
@@ -13579,6 +15109,8 @@
       <c r="H302" t="n">
         <v>50.4</v>
       </c>
+      <c r="I302"/>
+      <c r="J302"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n">
@@ -13587,6 +15119,7 @@
       <c r="B303" t="n">
         <v>48.5</v>
       </c>
+      <c r="C303"/>
       <c r="D303" t="n">
         <v>46.3</v>
       </c>
@@ -13602,6 +15135,8 @@
       <c r="H303" t="n">
         <v>52</v>
       </c>
+      <c r="I303"/>
+      <c r="J303"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n">
@@ -13610,6 +15145,7 @@
       <c r="B304" t="n">
         <v>47.3</v>
       </c>
+      <c r="C304"/>
       <c r="D304" t="n">
         <v>44.7</v>
       </c>
@@ -13625,6 +15161,8 @@
       <c r="H304" t="n">
         <v>51.1</v>
       </c>
+      <c r="I304"/>
+      <c r="J304"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n">
@@ -13633,6 +15171,7 @@
       <c r="B305" t="n">
         <v>45.8</v>
       </c>
+      <c r="C305"/>
       <c r="D305" t="n">
         <v>44.5</v>
       </c>
@@ -13648,6 +15187,8 @@
       <c r="H305" t="n">
         <v>46.8</v>
       </c>
+      <c r="I305"/>
+      <c r="J305"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n">
@@ -13656,6 +15197,7 @@
       <c r="B306" t="n">
         <v>44.8</v>
       </c>
+      <c r="C306"/>
       <c r="D306" t="n">
         <v>43.2</v>
       </c>
@@ -13671,6 +15213,8 @@
       <c r="H306" t="n">
         <v>45.9</v>
       </c>
+      <c r="I306"/>
+      <c r="J306"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n">
@@ -13679,6 +15223,7 @@
       <c r="B307" t="n">
         <v>43.4</v>
       </c>
+      <c r="C307"/>
       <c r="D307" t="n">
         <v>40.6</v>
       </c>
@@ -13694,6 +15239,8 @@
       <c r="H307" t="n">
         <v>43.8</v>
       </c>
+      <c r="I307"/>
+      <c r="J307"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n">
@@ -13702,6 +15249,7 @@
       <c r="B308" t="n">
         <v>42.7</v>
       </c>
+      <c r="C308"/>
       <c r="D308" t="n">
         <v>38.8</v>
       </c>
@@ -13717,6 +15265,8 @@
       <c r="H308" t="n">
         <v>44.5</v>
       </c>
+      <c r="I308"/>
+      <c r="J308"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n">
@@ -13725,6 +15275,7 @@
       <c r="B309" t="n">
         <v>43.5</v>
       </c>
+      <c r="C309"/>
       <c r="D309" t="n">
         <v>39.1</v>
       </c>
@@ -13740,6 +15291,8 @@
       <c r="H309" t="n">
         <v>45.4</v>
       </c>
+      <c r="I309"/>
+      <c r="J309"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n">
@@ -13748,6 +15301,7 @@
       <c r="B310" t="n">
         <v>43.4</v>
       </c>
+      <c r="C310"/>
       <c r="D310" t="n">
         <v>39.6</v>
       </c>
@@ -13763,6 +15317,8 @@
       <c r="H310" t="n">
         <v>46.8</v>
       </c>
+      <c r="I310"/>
+      <c r="J310"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n">
@@ -13771,6 +15327,7 @@
       <c r="B311" t="n">
         <v>43.1</v>
       </c>
+      <c r="C311"/>
       <c r="D311" t="n">
         <v>40.8</v>
       </c>
@@ -13786,6 +15343,8 @@
       <c r="H311" t="n">
         <v>44.9</v>
       </c>
+      <c r="I311"/>
+      <c r="J311"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n">
@@ -13794,6 +15353,7 @@
       <c r="B312" t="n">
         <v>44.2</v>
       </c>
+      <c r="C312"/>
       <c r="D312" t="n">
         <v>42.6</v>
       </c>
@@ -13809,6 +15369,8 @@
       <c r="H312" t="n">
         <v>44.4</v>
       </c>
+      <c r="I312"/>
+      <c r="J312"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n">
@@ -13817,6 +15379,7 @@
       <c r="B313" t="n">
         <v>44.4</v>
       </c>
+      <c r="C313"/>
       <c r="D313" t="n">
         <v>43.3</v>
       </c>
@@ -13832,6 +15395,8 @@
       <c r="H313" t="n">
         <v>45.3</v>
       </c>
+      <c r="I313"/>
+      <c r="J313"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n">
@@ -13840,6 +15405,7 @@
       <c r="B314" t="n">
         <v>46.6</v>
       </c>
+      <c r="C314"/>
       <c r="D314" t="n">
         <v>45.5</v>
       </c>
@@ -13855,6 +15421,8 @@
       <c r="H314" t="n">
         <v>48.5</v>
       </c>
+      <c r="I314"/>
+      <c r="J314"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n">
@@ -13863,6 +15431,7 @@
       <c r="B315" t="n">
         <v>46.5</v>
       </c>
+      <c r="C315"/>
       <c r="D315" t="n">
         <v>42.5</v>
       </c>
@@ -13878,6 +15447,8 @@
       <c r="H315" t="n">
         <v>48.7</v>
       </c>
+      <c r="I315"/>
+      <c r="J315"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n">
@@ -13886,6 +15457,7 @@
       <c r="B316" t="n">
         <v>46.1</v>
       </c>
+      <c r="C316"/>
       <c r="D316" t="n">
         <v>41.9</v>
       </c>
@@ -13901,6 +15473,8 @@
       <c r="H316" t="n">
         <v>50.4</v>
       </c>
+      <c r="I316"/>
+      <c r="J316"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n">
@@ -13909,6 +15483,7 @@
       <c r="B317" t="n">
         <v>45.7</v>
       </c>
+      <c r="C317"/>
       <c r="D317" t="n">
         <v>42.5</v>
       </c>
@@ -13924,6 +15499,8 @@
       <c r="H317" t="n">
         <v>47.3</v>
       </c>
+      <c r="I317"/>
+      <c r="J317"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n">
@@ -13932,6 +15509,7 @@
       <c r="B318" t="n">
         <v>47.3</v>
       </c>
+      <c r="C318"/>
       <c r="D318" t="n">
         <v>45.4</v>
       </c>
@@ -13947,6 +15525,8 @@
       <c r="H318" t="n">
         <v>45.6</v>
       </c>
+      <c r="I318"/>
+      <c r="J318"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n">
@@ -13955,6 +15535,7 @@
       <c r="B319" t="n">
         <v>45.8</v>
       </c>
+      <c r="C319"/>
       <c r="D319" t="n">
         <v>43.5</v>
       </c>
@@ -13970,6 +15551,8 @@
       <c r="H319" t="n">
         <v>45.7</v>
       </c>
+      <c r="I319"/>
+      <c r="J319"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n">
@@ -13978,6 +15561,7 @@
       <c r="B320" t="n">
         <v>45.8</v>
       </c>
+      <c r="C320"/>
       <c r="D320" t="n">
         <v>43.2</v>
       </c>
@@ -13993,6 +15577,8 @@
       <c r="H320" t="n">
         <v>47.4</v>
       </c>
+      <c r="I320"/>
+      <c r="J320"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n">
@@ -14001,6 +15587,7 @@
       <c r="B321" t="n">
         <v>45.8</v>
       </c>
+      <c r="C321"/>
       <c r="D321" t="n">
         <v>42.4</v>
       </c>
@@ -14016,6 +15603,8 @@
       <c r="H321" t="n">
         <v>49.4</v>
       </c>
+      <c r="I321"/>
+      <c r="J321"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n">
@@ -14024,6 +15613,7 @@
       <c r="B322" t="n">
         <v>45</v>
       </c>
+      <c r="C322"/>
       <c r="D322" t="n">
         <v>40.6</v>
       </c>
@@ -14039,6 +15629,8 @@
       <c r="H322" t="n">
         <v>48.3</v>
       </c>
+      <c r="I322"/>
+      <c r="J322"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n">
@@ -14047,6 +15639,7 @@
       <c r="B323" t="n">
         <v>46</v>
       </c>
+      <c r="C323"/>
       <c r="D323" t="n">
         <v>43</v>
       </c>
@@ -14062,6 +15655,8 @@
       <c r="H323" t="n">
         <v>46.9</v>
       </c>
+      <c r="I323"/>
+      <c r="J323"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n">
@@ -14070,6 +15665,7 @@
       <c r="B324" t="n">
         <v>45.2</v>
       </c>
+      <c r="C324"/>
       <c r="D324" t="n">
         <v>43</v>
       </c>
@@ -14085,6 +15681,8 @@
       <c r="H324" t="n">
         <v>44.5</v>
       </c>
+      <c r="I324"/>
+      <c r="J324"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n">
@@ -14093,6 +15691,7 @@
       <c r="B325" t="n">
         <v>45.1</v>
       </c>
+      <c r="C325"/>
       <c r="D325" t="n">
         <v>42.5</v>
       </c>
@@ -14108,6 +15707,8 @@
       <c r="H325" t="n">
         <v>46.2</v>
       </c>
+      <c r="I325"/>
+      <c r="J325"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n">
@@ -14116,6 +15717,7 @@
       <c r="B326" t="n">
         <v>46.6</v>
       </c>
+      <c r="C326"/>
       <c r="D326" t="n">
         <v>45</v>
       </c>
@@ -14131,6 +15733,8 @@
       <c r="H326" t="n">
         <v>46.3</v>
       </c>
+      <c r="I326"/>
+      <c r="J326"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n">
@@ -14139,6 +15743,7 @@
       <c r="B327" t="n">
         <v>47.6</v>
       </c>
+      <c r="C327"/>
       <c r="D327" t="n">
         <v>46.5</v>
       </c>
@@ -14154,6 +15759,8 @@
       <c r="H327" t="n">
         <v>47.4</v>
       </c>
+      <c r="I327"/>
+      <c r="J327"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n">
@@ -14162,6 +15769,7 @@
       <c r="B328" t="n">
         <v>48.6</v>
       </c>
+      <c r="C328"/>
       <c r="D328" t="n">
         <v>48.3</v>
       </c>
@@ -14177,6 +15785,8 @@
       <c r="H328" t="n">
         <v>46.6</v>
       </c>
+      <c r="I328"/>
+      <c r="J328"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n">
@@ -14185,6 +15795,7 @@
       <c r="B329" t="n">
         <v>49</v>
       </c>
+      <c r="C329"/>
       <c r="D329" t="n">
         <v>48.4</v>
       </c>
@@ -14200,6 +15811,8 @@
       <c r="H329" t="n">
         <v>49.3</v>
       </c>
+      <c r="I329"/>
+      <c r="J329"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n">
@@ -14208,6 +15821,7 @@
       <c r="B330" t="n">
         <v>49.4</v>
       </c>
+      <c r="C330"/>
       <c r="D330" t="n">
         <v>48.3</v>
       </c>
@@ -14223,6 +15837,8 @@
       <c r="H330" t="n">
         <v>49.2</v>
       </c>
+      <c r="I330"/>
+      <c r="J330"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n">
@@ -14231,6 +15847,7 @@
       <c r="B331" t="n">
         <v>49.5</v>
       </c>
+      <c r="C331"/>
       <c r="D331" t="n">
         <v>49</v>
       </c>
@@ -14246,6 +15863,8 @@
       <c r="H331" t="n">
         <v>48.4</v>
       </c>
+      <c r="I331"/>
+      <c r="J331"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n">
@@ -14254,6 +15873,7 @@
       <c r="B332" t="n">
         <v>49.8</v>
       </c>
+      <c r="C332"/>
       <c r="D332" t="n">
         <v>49.1</v>
       </c>
@@ -14269,6 +15889,8 @@
       <c r="H332" t="n">
         <v>49.8</v>
       </c>
+      <c r="I332"/>
+      <c r="J332"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n">
@@ -14277,6 +15899,7 @@
       <c r="B333" t="n">
         <v>50.7</v>
       </c>
+      <c r="C333"/>
       <c r="D333" t="n">
         <v>49.8</v>
       </c>
@@ -14292,6 +15915,8 @@
       <c r="H333" t="n">
         <v>50.4</v>
       </c>
+      <c r="I333"/>
+      <c r="J333"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n">
@@ -14300,6 +15925,7 @@
       <c r="B334" t="n">
         <v>49.8</v>
       </c>
+      <c r="C334"/>
       <c r="D334" t="n">
         <v>49.5</v>
       </c>
@@ -14315,6 +15941,8 @@
       <c r="H334" t="n">
         <v>49</v>
       </c>
+      <c r="I334"/>
+      <c r="J334"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n">
@@ -14323,6 +15951,7 @@
       <c r="B335" t="n">
         <v>50</v>
       </c>
+      <c r="C335"/>
       <c r="D335" t="n">
         <v>49.6</v>
       </c>
@@ -14338,6 +15967,8 @@
       <c r="H335" t="n">
         <v>49.9</v>
       </c>
+      <c r="I335"/>
+      <c r="J335"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n">
@@ -14346,6 +15977,7 @@
       <c r="B336" t="n">
         <v>49.6</v>
       </c>
+      <c r="C336"/>
       <c r="D336" t="n">
         <v>48.2</v>
       </c>
@@ -14361,6 +15993,8 @@
       <c r="H336" t="n">
         <v>50.6</v>
       </c>
+      <c r="I336"/>
+      <c r="J336"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n">
@@ -14369,6 +16003,7 @@
       <c r="B337" t="n">
         <v>48.8</v>
       </c>
+      <c r="C337"/>
       <c r="D337" t="n">
         <v>47</v>
       </c>
@@ -14384,6 +16019,8 @@
       <c r="H337" t="n">
         <v>47.9</v>
       </c>
+      <c r="I337"/>
+      <c r="J337"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n">
@@ -14392,6 +16029,7 @@
       <c r="B338" t="n">
         <v>49.5</v>
       </c>
+      <c r="C338"/>
       <c r="D338" t="n">
         <v>49.1</v>
       </c>
@@ -14407,6 +16045,8 @@
       <c r="H338" t="n">
         <v>48.1</v>
       </c>
+      <c r="I338"/>
+      <c r="J338"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n">
@@ -14415,6 +16055,7 @@
       <c r="B339" t="n">
         <v>50.8</v>
       </c>
+      <c r="C339"/>
       <c r="D339" t="n">
         <v>50.9</v>
       </c>
@@ -14430,6 +16071,8 @@
       <c r="H339" t="n">
         <v>50.6</v>
       </c>
+      <c r="I339"/>
+      <c r="J339"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n">
@@ -14438,6 +16081,7 @@
       <c r="B340" t="n">
         <v>51.6</v>
       </c>
+      <c r="C340"/>
       <c r="D340" t="n">
         <v>52.2</v>
       </c>
@@ -14453,6 +16097,8 @@
       <c r="H340" t="n">
         <v>51.3</v>
       </c>
+      <c r="I340"/>
+      <c r="J340"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n">
@@ -14461,6 +16107,7 @@
       <c r="B341" t="n">
         <v>52.2</v>
       </c>
+      <c r="C341"/>
       <c r="D341" t="n">
         <v>51.4</v>
       </c>
@@ -14476,6 +16123,8 @@
       <c r="H341" t="n">
         <v>52.1</v>
       </c>
+      <c r="I341"/>
+      <c r="J341"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n">
@@ -14484,6 +16133,7 @@
       <c r="B342" t="n">
         <v>51.6</v>
       </c>
+      <c r="C342"/>
       <c r="D342" t="n">
         <v>50.1</v>
       </c>
@@ -14499,6 +16149,8 @@
       <c r="H342" t="n">
         <v>52.9</v>
       </c>
+      <c r="I342"/>
+      <c r="J342"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n">
@@ -14507,6 +16159,9 @@
       <c r="B343" t="n">
         <v>51.4</v>
       </c>
+      <c r="C343"/>
+      <c r="D343"/>
+      <c r="E343"/>
       <c r="F343" t="n">
         <v>49.7</v>
       </c>
@@ -14516,6 +16171,34 @@
       <c r="H343" t="n">
         <v>52.2</v>
       </c>
+      <c r="I343"/>
+      <c r="J343"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B344" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="C344"/>
+      <c r="D344" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E344" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F344" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G344" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H344" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I344"/>
+      <c r="J344"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
